--- a/DND05S.xlsx
+++ b/DND05S.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1818" uniqueCount="658">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1818" uniqueCount="657">
   <si>
     <t/>
   </si>
@@ -337,9 +337,6 @@
     <t>RINSO PW.CLN BTL 650</t>
   </si>
   <si>
-    <t>TG</t>
-  </si>
-  <si>
     <t>20141369</t>
   </si>
   <si>
@@ -568,24 +565,30 @@
     <t>ROYALE SOFT P.DW 650</t>
   </si>
   <si>
+    <t>20104951</t>
+  </si>
+  <si>
+    <t>ROYALE HJB BLCK.V650</t>
+  </si>
+  <si>
+    <t>20091457</t>
+  </si>
+  <si>
+    <t>ROYALE SOFT BS 650</t>
+  </si>
+  <si>
+    <t>20098312</t>
+  </si>
+  <si>
+    <t>ROYALE PINK STN 650</t>
+  </si>
+  <si>
     <t>20113101</t>
   </si>
   <si>
     <t>ROYALE SWT FLORL 680</t>
   </si>
   <si>
-    <t>20104951</t>
-  </si>
-  <si>
-    <t>ROYALE HJB BLCK.V650</t>
-  </si>
-  <si>
-    <t>20091457</t>
-  </si>
-  <si>
-    <t>ROYALE SOFT BS 650</t>
-  </si>
-  <si>
     <t>20128706</t>
   </si>
   <si>
@@ -596,12 +599,6 @@
   </si>
   <si>
     <t>ROYALE SUNNY DAY 680</t>
-  </si>
-  <si>
-    <t>20098312</t>
-  </si>
-  <si>
-    <t>ROYALE PINK STN 650</t>
   </si>
   <si>
     <t>20126740</t>
@@ -3304,15 +3301,15 @@
         <v>32</v>
       </c>
       <c r="F46" s="1" t="s">
-        <v>108</v>
+        <v>21</v>
       </c>
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A47" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="B47" s="1" t="s">
         <v>109</v>
-      </c>
-      <c r="B47" s="1" t="s">
-        <v>110</v>
       </c>
       <c r="C47" s="1" t="s">
         <v>3</v>
@@ -3324,15 +3321,15 @@
         <v>35</v>
       </c>
       <c r="F47" s="1" t="s">
-        <v>108</v>
+        <v>21</v>
       </c>
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A48" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="B48" s="1" t="s">
         <v>111</v>
-      </c>
-      <c r="B48" s="1" t="s">
-        <v>112</v>
       </c>
       <c r="C48" s="1" t="s">
         <v>3</v>
@@ -3349,10 +3346,10 @@
     </row>
     <row r="49" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A49" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="B49" s="1" t="s">
         <v>113</v>
-      </c>
-      <c r="B49" s="1" t="s">
-        <v>114</v>
       </c>
       <c r="C49" s="1" t="s">
         <v>3</v>
@@ -3369,10 +3366,10 @@
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A50" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="B50" s="1" t="s">
         <v>115</v>
-      </c>
-      <c r="B50" s="1" t="s">
-        <v>116</v>
       </c>
       <c r="C50" s="1" t="s">
         <v>3</v>
@@ -3389,10 +3386,10 @@
     </row>
     <row r="51" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A51" s="1" t="s">
+        <v>116</v>
+      </c>
+      <c r="B51" s="1" t="s">
         <v>117</v>
-      </c>
-      <c r="B51" s="1" t="s">
-        <v>118</v>
       </c>
       <c r="C51" s="1" t="s">
         <v>3</v>
@@ -3409,10 +3406,10 @@
     </row>
     <row r="52" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A52" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="B52" s="1" t="s">
         <v>119</v>
-      </c>
-      <c r="B52" s="1" t="s">
-        <v>120</v>
       </c>
       <c r="C52" s="1" t="s">
         <v>3</v>
@@ -3429,10 +3426,10 @@
     </row>
     <row r="53" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A53" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="B53" s="1" t="s">
         <v>121</v>
-      </c>
-      <c r="B53" s="1" t="s">
-        <v>122</v>
       </c>
       <c r="C53" s="1" t="s">
         <v>3</v>
@@ -3449,10 +3446,10 @@
     </row>
     <row r="54" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A54" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="B54" s="1" t="s">
         <v>123</v>
-      </c>
-      <c r="B54" s="1" t="s">
-        <v>124</v>
       </c>
       <c r="C54" s="1" t="s">
         <v>3</v>
@@ -3469,10 +3466,10 @@
     </row>
     <row r="55" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A55" s="1" t="s">
+        <v>124</v>
+      </c>
+      <c r="B55" s="1" t="s">
         <v>125</v>
-      </c>
-      <c r="B55" s="1" t="s">
-        <v>126</v>
       </c>
       <c r="C55" s="1" t="s">
         <v>3</v>
@@ -3489,10 +3486,10 @@
     </row>
     <row r="56" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A56" s="1" t="s">
+        <v>126</v>
+      </c>
+      <c r="B56" s="1" t="s">
         <v>127</v>
-      </c>
-      <c r="B56" s="1" t="s">
-        <v>128</v>
       </c>
       <c r="C56" s="1" t="s">
         <v>3</v>
@@ -3509,10 +3506,10 @@
     </row>
     <row r="57" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A57" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="B57" s="1" t="s">
         <v>129</v>
-      </c>
-      <c r="B57" s="1" t="s">
-        <v>130</v>
       </c>
       <c r="C57" s="1" t="s">
         <v>3</v>
@@ -3529,10 +3526,10 @@
     </row>
     <row r="58" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A58" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="B58" s="1" t="s">
         <v>131</v>
-      </c>
-      <c r="B58" s="1" t="s">
-        <v>132</v>
       </c>
       <c r="C58" s="1" t="s">
         <v>3</v>
@@ -3549,10 +3546,10 @@
     </row>
     <row r="59" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A59" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="B59" s="1" t="s">
         <v>133</v>
-      </c>
-      <c r="B59" s="1" t="s">
-        <v>134</v>
       </c>
       <c r="C59" s="1" t="s">
         <v>3</v>
@@ -3569,10 +3566,10 @@
     </row>
     <row r="60" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A60" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="B60" s="1" t="s">
         <v>135</v>
-      </c>
-      <c r="B60" s="1" t="s">
-        <v>136</v>
       </c>
       <c r="C60" s="1" t="s">
         <v>3</v>
@@ -3589,10 +3586,10 @@
     </row>
     <row r="61" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A61" s="1" t="s">
+        <v>136</v>
+      </c>
+      <c r="B61" s="1" t="s">
         <v>137</v>
-      </c>
-      <c r="B61" s="1" t="s">
-        <v>138</v>
       </c>
       <c r="C61" s="1" t="s">
         <v>3</v>
@@ -3609,10 +3606,10 @@
     </row>
     <row r="62" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A62" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="B62" s="1" t="s">
         <v>139</v>
-      </c>
-      <c r="B62" s="1" t="s">
-        <v>140</v>
       </c>
       <c r="C62" s="1" t="s">
         <v>3</v>
@@ -3629,10 +3626,10 @@
     </row>
     <row r="63" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A63" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="B63" s="1" t="s">
         <v>141</v>
-      </c>
-      <c r="B63" s="1" t="s">
-        <v>142</v>
       </c>
       <c r="C63" s="1" t="s">
         <v>3</v>
@@ -3649,10 +3646,10 @@
     </row>
     <row r="64" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A64" s="1" t="s">
+        <v>142</v>
+      </c>
+      <c r="B64" s="1" t="s">
         <v>143</v>
-      </c>
-      <c r="B64" s="1" t="s">
-        <v>144</v>
       </c>
       <c r="C64" s="1" t="s">
         <v>3</v>
@@ -3669,16 +3666,16 @@
     </row>
     <row r="65" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A65" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="B65" s="1" t="s">
         <v>145</v>
       </c>
-      <c r="B65" s="1" t="s">
+      <c r="C65" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D65" s="1" t="s">
         <v>146</v>
-      </c>
-      <c r="C65" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D65" s="1" t="s">
-        <v>147</v>
       </c>
       <c r="E65" s="1" t="s">
         <v>4</v>
@@ -3689,16 +3686,16 @@
     </row>
     <row r="66" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A66" s="1" t="s">
+        <v>147</v>
+      </c>
+      <c r="B66" s="1" t="s">
         <v>148</v>
       </c>
-      <c r="B66" s="1" t="s">
-        <v>149</v>
-      </c>
       <c r="C66" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D66" s="1" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="E66" s="1" t="s">
         <v>8</v>
@@ -3709,16 +3706,16 @@
     </row>
     <row r="67" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A67" s="1" t="s">
+        <v>149</v>
+      </c>
+      <c r="B67" s="1" t="s">
         <v>150</v>
       </c>
-      <c r="B67" s="1" t="s">
-        <v>151</v>
-      </c>
       <c r="C67" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D67" s="1" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="E67" s="1" t="s">
         <v>11</v>
@@ -3729,16 +3726,16 @@
     </row>
     <row r="68" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A68" s="1" t="s">
+        <v>151</v>
+      </c>
+      <c r="B68" s="1" t="s">
         <v>152</v>
       </c>
-      <c r="B68" s="1" t="s">
-        <v>153</v>
-      </c>
       <c r="C68" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D68" s="1" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="E68" s="1" t="s">
         <v>14</v>
@@ -3749,16 +3746,16 @@
     </row>
     <row r="69" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A69" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="B69" s="1" t="s">
         <v>154</v>
       </c>
-      <c r="B69" s="1" t="s">
-        <v>155</v>
-      </c>
       <c r="C69" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D69" s="1" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="E69" s="1" t="s">
         <v>18</v>
@@ -3769,16 +3766,16 @@
     </row>
     <row r="70" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A70" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="B70" s="1" t="s">
         <v>156</v>
       </c>
-      <c r="B70" s="1" t="s">
+      <c r="C70" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D70" s="1" t="s">
         <v>157</v>
-      </c>
-      <c r="C70" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D70" s="1" t="s">
-        <v>158</v>
       </c>
       <c r="E70" s="1" t="s">
         <v>4</v>
@@ -3789,16 +3786,16 @@
     </row>
     <row r="71" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A71" s="1" t="s">
+        <v>158</v>
+      </c>
+      <c r="B71" s="1" t="s">
         <v>159</v>
       </c>
-      <c r="B71" s="1" t="s">
-        <v>160</v>
-      </c>
       <c r="C71" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D71" s="1" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="E71" s="1" t="s">
         <v>8</v>
@@ -3809,16 +3806,16 @@
     </row>
     <row r="72" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A72" s="1" t="s">
+        <v>160</v>
+      </c>
+      <c r="B72" s="1" t="s">
         <v>161</v>
       </c>
-      <c r="B72" s="1" t="s">
-        <v>162</v>
-      </c>
       <c r="C72" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D72" s="1" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="E72" s="1" t="s">
         <v>11</v>
@@ -3829,16 +3826,16 @@
     </row>
     <row r="73" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A73" s="1" t="s">
+        <v>162</v>
+      </c>
+      <c r="B73" s="1" t="s">
         <v>163</v>
       </c>
-      <c r="B73" s="1" t="s">
-        <v>164</v>
-      </c>
       <c r="C73" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D73" s="1" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="E73" s="1" t="s">
         <v>14</v>
@@ -3849,16 +3846,16 @@
     </row>
     <row r="74" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A74" s="1" t="s">
+        <v>164</v>
+      </c>
+      <c r="B74" s="1" t="s">
         <v>165</v>
       </c>
-      <c r="B74" s="1" t="s">
-        <v>166</v>
-      </c>
       <c r="C74" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D74" s="1" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="E74" s="1" t="s">
         <v>18</v>
@@ -3869,16 +3866,16 @@
     </row>
     <row r="75" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A75" s="1" t="s">
+        <v>166</v>
+      </c>
+      <c r="B75" s="1" t="s">
         <v>167</v>
       </c>
-      <c r="B75" s="1" t="s">
+      <c r="C75" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D75" s="1" t="s">
         <v>168</v>
-      </c>
-      <c r="C75" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D75" s="1" t="s">
-        <v>169</v>
       </c>
       <c r="E75" s="1" t="s">
         <v>4</v>
@@ -3889,16 +3886,16 @@
     </row>
     <row r="76" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A76" s="1" t="s">
+        <v>169</v>
+      </c>
+      <c r="B76" s="1" t="s">
         <v>170</v>
       </c>
-      <c r="B76" s="1" t="s">
-        <v>171</v>
-      </c>
       <c r="C76" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D76" s="1" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="E76" s="1" t="s">
         <v>8</v>
@@ -3909,16 +3906,16 @@
     </row>
     <row r="77" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A77" s="1" t="s">
+        <v>171</v>
+      </c>
+      <c r="B77" s="1" t="s">
         <v>172</v>
       </c>
-      <c r="B77" s="1" t="s">
-        <v>173</v>
-      </c>
       <c r="C77" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D77" s="1" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="E77" s="1" t="s">
         <v>11</v>
@@ -3929,16 +3926,16 @@
     </row>
     <row r="78" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A78" s="1" t="s">
+        <v>173</v>
+      </c>
+      <c r="B78" s="1" t="s">
         <v>174</v>
       </c>
-      <c r="B78" s="1" t="s">
-        <v>175</v>
-      </c>
       <c r="C78" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D78" s="1" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="E78" s="1" t="s">
         <v>14</v>
@@ -3949,16 +3946,16 @@
     </row>
     <row r="79" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A79" s="1" t="s">
+        <v>175</v>
+      </c>
+      <c r="B79" s="1" t="s">
         <v>176</v>
       </c>
-      <c r="B79" s="1" t="s">
-        <v>177</v>
-      </c>
       <c r="C79" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D79" s="1" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="E79" s="1" t="s">
         <v>18</v>
@@ -3969,16 +3966,16 @@
     </row>
     <row r="80" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A80" s="1" t="s">
+        <v>177</v>
+      </c>
+      <c r="B80" s="1" t="s">
         <v>178</v>
       </c>
-      <c r="B80" s="1" t="s">
-        <v>179</v>
-      </c>
       <c r="C80" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D80" s="1" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="E80" s="1" t="s">
         <v>32</v>
@@ -3989,16 +3986,16 @@
     </row>
     <row r="81" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A81" s="1" t="s">
+        <v>179</v>
+      </c>
+      <c r="B81" s="1" t="s">
         <v>180</v>
       </c>
-      <c r="B81" s="1" t="s">
+      <c r="C81" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D81" s="1" t="s">
         <v>181</v>
-      </c>
-      <c r="C81" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D81" s="1" t="s">
-        <v>182</v>
       </c>
       <c r="E81" s="1" t="s">
         <v>4</v>
@@ -4009,16 +4006,16 @@
     </row>
     <row r="82" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A82" s="1" t="s">
+        <v>182</v>
+      </c>
+      <c r="B82" s="1" t="s">
         <v>183</v>
       </c>
-      <c r="B82" s="1" t="s">
-        <v>184</v>
-      </c>
       <c r="C82" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D82" s="1" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="E82" s="1" t="s">
         <v>8</v>
@@ -4029,16 +4026,16 @@
     </row>
     <row r="83" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A83" s="1" t="s">
+        <v>184</v>
+      </c>
+      <c r="B83" s="1" t="s">
         <v>185</v>
       </c>
-      <c r="B83" s="1" t="s">
-        <v>186</v>
-      </c>
       <c r="C83" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D83" s="1" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="E83" s="1" t="s">
         <v>11</v>
@@ -4049,16 +4046,16 @@
     </row>
     <row r="84" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A84" s="1" t="s">
+        <v>186</v>
+      </c>
+      <c r="B84" s="1" t="s">
         <v>187</v>
       </c>
-      <c r="B84" s="1" t="s">
-        <v>188</v>
-      </c>
       <c r="C84" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D84" s="1" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="E84" s="1" t="s">
         <v>14</v>
@@ -4069,16 +4066,16 @@
     </row>
     <row r="85" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A85" s="1" t="s">
+        <v>188</v>
+      </c>
+      <c r="B85" s="1" t="s">
         <v>189</v>
       </c>
-      <c r="B85" s="1" t="s">
-        <v>190</v>
-      </c>
       <c r="C85" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D85" s="1" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="E85" s="1" t="s">
         <v>18</v>
@@ -4089,16 +4086,16 @@
     </row>
     <row r="86" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A86" s="1" t="s">
+        <v>190</v>
+      </c>
+      <c r="B86" s="1" t="s">
         <v>191</v>
       </c>
-      <c r="B86" s="1" t="s">
-        <v>192</v>
-      </c>
       <c r="C86" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D86" s="1" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="E86" s="1" t="s">
         <v>32</v>
@@ -4109,16 +4106,16 @@
     </row>
     <row r="87" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A87" s="1" t="s">
+        <v>192</v>
+      </c>
+      <c r="B87" s="1" t="s">
         <v>193</v>
       </c>
-      <c r="B87" s="1" t="s">
-        <v>194</v>
-      </c>
       <c r="C87" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D87" s="1" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="E87" s="1" t="s">
         <v>35</v>
@@ -4129,16 +4126,16 @@
     </row>
     <row r="88" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A88" s="1" t="s">
+        <v>194</v>
+      </c>
+      <c r="B88" s="1" t="s">
         <v>195</v>
       </c>
-      <c r="B88" s="1" t="s">
-        <v>196</v>
-      </c>
       <c r="C88" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D88" s="1" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="E88" s="1" t="s">
         <v>38</v>
@@ -4149,16 +4146,16 @@
     </row>
     <row r="89" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A89" s="1" t="s">
+        <v>196</v>
+      </c>
+      <c r="B89" s="1" t="s">
         <v>197</v>
       </c>
-      <c r="B89" s="1" t="s">
-        <v>198</v>
-      </c>
       <c r="C89" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D89" s="1" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="E89" s="1" t="s">
         <v>58</v>
@@ -4169,36 +4166,36 @@
     </row>
     <row r="90" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A90" s="1" t="s">
+        <v>198</v>
+      </c>
+      <c r="B90" s="1" t="s">
         <v>199</v>
       </c>
-      <c r="B90" s="1" t="s">
+      <c r="C90" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D90" s="1" t="s">
         <v>200</v>
-      </c>
-      <c r="C90" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D90" s="1" t="s">
-        <v>201</v>
       </c>
       <c r="E90" s="1" t="s">
         <v>4</v>
       </c>
       <c r="F90" s="1" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
     </row>
     <row r="91" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A91" s="1" t="s">
+        <v>202</v>
+      </c>
+      <c r="B91" s="1" t="s">
         <v>203</v>
       </c>
-      <c r="B91" s="1" t="s">
-        <v>204</v>
-      </c>
       <c r="C91" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D91" s="1" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="E91" s="1" t="s">
         <v>8</v>
@@ -4209,16 +4206,16 @@
     </row>
     <row r="92" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A92" s="1" t="s">
+        <v>204</v>
+      </c>
+      <c r="B92" s="1" t="s">
         <v>205</v>
       </c>
-      <c r="B92" s="1" t="s">
-        <v>206</v>
-      </c>
       <c r="C92" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D92" s="1" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="E92" s="1" t="s">
         <v>11</v>
@@ -4229,76 +4226,76 @@
     </row>
     <row r="93" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A93" s="1" t="s">
+        <v>206</v>
+      </c>
+      <c r="B93" s="1" t="s">
         <v>207</v>
       </c>
-      <c r="B93" s="1" t="s">
-        <v>208</v>
-      </c>
       <c r="C93" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D93" s="1" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="E93" s="1" t="s">
         <v>14</v>
       </c>
       <c r="F93" s="1" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
     </row>
     <row r="94" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A94" s="1" t="s">
+        <v>208</v>
+      </c>
+      <c r="B94" s="1" t="s">
         <v>209</v>
       </c>
-      <c r="B94" s="1" t="s">
-        <v>210</v>
-      </c>
       <c r="C94" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D94" s="1" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="E94" s="1" t="s">
         <v>18</v>
       </c>
       <c r="F94" s="1" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
     </row>
     <row r="95" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A95" s="1" t="s">
+        <v>210</v>
+      </c>
+      <c r="B95" s="1" t="s">
         <v>211</v>
       </c>
-      <c r="B95" s="1" t="s">
-        <v>212</v>
-      </c>
       <c r="C95" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D95" s="1" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="E95" s="1" t="s">
         <v>32</v>
       </c>
       <c r="F95" s="1" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
     </row>
     <row r="96" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A96" s="1" t="s">
+        <v>212</v>
+      </c>
+      <c r="B96" s="1" t="s">
         <v>213</v>
       </c>
-      <c r="B96" s="1" t="s">
-        <v>214</v>
-      </c>
       <c r="C96" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D96" s="1" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="E96" s="1" t="s">
         <v>35</v>
@@ -4309,16 +4306,16 @@
     </row>
     <row r="97" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A97" s="1" t="s">
+        <v>214</v>
+      </c>
+      <c r="B97" s="1" t="s">
         <v>215</v>
       </c>
-      <c r="B97" s="1" t="s">
-        <v>216</v>
-      </c>
       <c r="C97" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D97" s="1" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="E97" s="1" t="s">
         <v>38</v>
@@ -4329,16 +4326,16 @@
     </row>
     <row r="98" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A98" s="1" t="s">
+        <v>216</v>
+      </c>
+      <c r="B98" s="1" t="s">
         <v>217</v>
       </c>
-      <c r="B98" s="1" t="s">
-        <v>218</v>
-      </c>
       <c r="C98" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D98" s="1" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="E98" s="1" t="s">
         <v>58</v>
@@ -4349,16 +4346,16 @@
     </row>
     <row r="99" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A99" s="1" t="s">
+        <v>218</v>
+      </c>
+      <c r="B99" s="1" t="s">
         <v>219</v>
       </c>
-      <c r="B99" s="1" t="s">
+      <c r="C99" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D99" s="1" t="s">
         <v>220</v>
-      </c>
-      <c r="C99" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D99" s="1" t="s">
-        <v>221</v>
       </c>
       <c r="E99" s="1" t="s">
         <v>4</v>
@@ -4369,16 +4366,16 @@
     </row>
     <row r="100" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A100" s="1" t="s">
+        <v>221</v>
+      </c>
+      <c r="B100" s="1" t="s">
         <v>222</v>
       </c>
-      <c r="B100" s="1" t="s">
-        <v>223</v>
-      </c>
       <c r="C100" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D100" s="1" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="E100" s="1" t="s">
         <v>8</v>
@@ -4389,16 +4386,16 @@
     </row>
     <row r="101" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A101" s="1" t="s">
+        <v>223</v>
+      </c>
+      <c r="B101" s="1" t="s">
         <v>224</v>
       </c>
-      <c r="B101" s="1" t="s">
-        <v>225</v>
-      </c>
       <c r="C101" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D101" s="1" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="E101" s="1" t="s">
         <v>11</v>
@@ -4409,16 +4406,16 @@
     </row>
     <row r="102" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A102" s="1" t="s">
+        <v>225</v>
+      </c>
+      <c r="B102" s="1" t="s">
         <v>226</v>
       </c>
-      <c r="B102" s="1" t="s">
-        <v>227</v>
-      </c>
       <c r="C102" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D102" s="1" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="E102" s="1" t="s">
         <v>14</v>
@@ -4429,16 +4426,16 @@
     </row>
     <row r="103" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A103" s="1" t="s">
+        <v>227</v>
+      </c>
+      <c r="B103" s="1" t="s">
         <v>228</v>
       </c>
-      <c r="B103" s="1" t="s">
+      <c r="C103" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D103" s="1" t="s">
         <v>229</v>
-      </c>
-      <c r="C103" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D103" s="1" t="s">
-        <v>230</v>
       </c>
       <c r="E103" s="1" t="s">
         <v>4</v>
@@ -4449,16 +4446,16 @@
     </row>
     <row r="104" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A104" s="1" t="s">
+        <v>230</v>
+      </c>
+      <c r="B104" s="1" t="s">
         <v>231</v>
       </c>
-      <c r="B104" s="1" t="s">
-        <v>232</v>
-      </c>
       <c r="C104" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D104" s="1" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="E104" s="1" t="s">
         <v>8</v>
@@ -4469,16 +4466,16 @@
     </row>
     <row r="105" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A105" s="1" t="s">
+        <v>232</v>
+      </c>
+      <c r="B105" s="1" t="s">
         <v>233</v>
       </c>
-      <c r="B105" s="1" t="s">
-        <v>234</v>
-      </c>
       <c r="C105" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D105" s="1" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="E105" s="1" t="s">
         <v>11</v>
@@ -4489,16 +4486,16 @@
     </row>
     <row r="106" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A106" s="1" t="s">
+        <v>234</v>
+      </c>
+      <c r="B106" s="1" t="s">
         <v>235</v>
       </c>
-      <c r="B106" s="1" t="s">
-        <v>236</v>
-      </c>
       <c r="C106" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D106" s="1" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="E106" s="1" t="s">
         <v>14</v>
@@ -4509,16 +4506,16 @@
     </row>
     <row r="107" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A107" s="1" t="s">
+        <v>236</v>
+      </c>
+      <c r="B107" s="1" t="s">
         <v>237</v>
       </c>
-      <c r="B107" s="1" t="s">
+      <c r="C107" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D107" s="1" t="s">
         <v>238</v>
-      </c>
-      <c r="C107" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D107" s="1" t="s">
-        <v>239</v>
       </c>
       <c r="E107" s="1" t="s">
         <v>4</v>
@@ -4529,16 +4526,16 @@
     </row>
     <row r="108" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A108" s="1" t="s">
+        <v>239</v>
+      </c>
+      <c r="B108" s="1" t="s">
         <v>240</v>
       </c>
-      <c r="B108" s="1" t="s">
-        <v>241</v>
-      </c>
       <c r="C108" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D108" s="1" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="E108" s="1" t="s">
         <v>8</v>
@@ -4549,16 +4546,16 @@
     </row>
     <row r="109" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A109" s="1" t="s">
+        <v>241</v>
+      </c>
+      <c r="B109" s="1" t="s">
         <v>242</v>
       </c>
-      <c r="B109" s="1" t="s">
-        <v>243</v>
-      </c>
       <c r="C109" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D109" s="1" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="E109" s="1" t="s">
         <v>11</v>
@@ -4569,16 +4566,16 @@
     </row>
     <row r="110" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A110" s="1" t="s">
+        <v>243</v>
+      </c>
+      <c r="B110" s="1" t="s">
         <v>244</v>
       </c>
-      <c r="B110" s="1" t="s">
-        <v>245</v>
-      </c>
       <c r="C110" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D110" s="1" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="E110" s="1" t="s">
         <v>14</v>
@@ -4589,16 +4586,16 @@
     </row>
     <row r="111" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A111" s="1" t="s">
+        <v>245</v>
+      </c>
+      <c r="B111" s="1" t="s">
         <v>246</v>
       </c>
-      <c r="B111" s="1" t="s">
-        <v>247</v>
-      </c>
       <c r="C111" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D111" s="1" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="E111" s="1" t="s">
         <v>18</v>
@@ -4609,16 +4606,16 @@
     </row>
     <row r="112" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A112" s="1" t="s">
+        <v>247</v>
+      </c>
+      <c r="B112" s="1" t="s">
         <v>248</v>
       </c>
-      <c r="B112" s="1" t="s">
+      <c r="C112" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D112" s="1" t="s">
         <v>249</v>
-      </c>
-      <c r="C112" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D112" s="1" t="s">
-        <v>250</v>
       </c>
       <c r="E112" s="1" t="s">
         <v>4</v>
@@ -4629,16 +4626,16 @@
     </row>
     <row r="113" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A113" s="1" t="s">
+        <v>250</v>
+      </c>
+      <c r="B113" s="1" t="s">
         <v>251</v>
       </c>
-      <c r="B113" s="1" t="s">
-        <v>252</v>
-      </c>
       <c r="C113" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D113" s="1" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="E113" s="1" t="s">
         <v>8</v>
@@ -4649,16 +4646,16 @@
     </row>
     <row r="114" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A114" s="1" t="s">
+        <v>252</v>
+      </c>
+      <c r="B114" s="1" t="s">
         <v>253</v>
       </c>
-      <c r="B114" s="1" t="s">
-        <v>254</v>
-      </c>
       <c r="C114" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D114" s="1" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="E114" s="1" t="s">
         <v>11</v>
@@ -4669,16 +4666,16 @@
     </row>
     <row r="115" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A115" s="1" t="s">
+        <v>254</v>
+      </c>
+      <c r="B115" s="1" t="s">
         <v>255</v>
       </c>
-      <c r="B115" s="1" t="s">
-        <v>256</v>
-      </c>
       <c r="C115" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D115" s="1" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="E115" s="1" t="s">
         <v>14</v>
@@ -4689,16 +4686,16 @@
     </row>
     <row r="116" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A116" s="1" t="s">
+        <v>256</v>
+      </c>
+      <c r="B116" s="1" t="s">
         <v>257</v>
       </c>
-      <c r="B116" s="1" t="s">
-        <v>258</v>
-      </c>
       <c r="C116" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D116" s="1" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="E116" s="1" t="s">
         <v>18</v>
@@ -4709,36 +4706,36 @@
     </row>
     <row r="117" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A117" s="1" t="s">
+        <v>258</v>
+      </c>
+      <c r="B117" s="1" t="s">
         <v>259</v>
       </c>
-      <c r="B117" s="1" t="s">
+      <c r="C117" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D117" s="1" t="s">
         <v>260</v>
-      </c>
-      <c r="C117" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D117" s="1" t="s">
-        <v>261</v>
       </c>
       <c r="E117" s="1" t="s">
         <v>4</v>
       </c>
       <c r="F117" s="1" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
     </row>
     <row r="118" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A118" s="1" t="s">
+        <v>262</v>
+      </c>
+      <c r="B118" s="1" t="s">
         <v>263</v>
       </c>
-      <c r="B118" s="1" t="s">
-        <v>264</v>
-      </c>
       <c r="C118" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D118" s="1" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="E118" s="1" t="s">
         <v>8</v>
@@ -4749,16 +4746,16 @@
     </row>
     <row r="119" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A119" s="1" t="s">
+        <v>264</v>
+      </c>
+      <c r="B119" s="1" t="s">
         <v>265</v>
       </c>
-      <c r="B119" s="1" t="s">
-        <v>266</v>
-      </c>
       <c r="C119" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D119" s="1" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="E119" s="1" t="s">
         <v>11</v>
@@ -4769,16 +4766,16 @@
     </row>
     <row r="120" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A120" s="1" t="s">
+        <v>266</v>
+      </c>
+      <c r="B120" s="1" t="s">
         <v>267</v>
       </c>
-      <c r="B120" s="1" t="s">
-        <v>268</v>
-      </c>
       <c r="C120" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D120" s="1" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="E120" s="1" t="s">
         <v>14</v>
@@ -4789,16 +4786,16 @@
     </row>
     <row r="121" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A121" s="1" t="s">
+        <v>268</v>
+      </c>
+      <c r="B121" s="1" t="s">
         <v>269</v>
       </c>
-      <c r="B121" s="1" t="s">
-        <v>270</v>
-      </c>
       <c r="C121" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D121" s="1" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="E121" s="1" t="s">
         <v>18</v>
@@ -4809,16 +4806,16 @@
     </row>
     <row r="122" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A122" s="1" t="s">
+        <v>270</v>
+      </c>
+      <c r="B122" s="1" t="s">
         <v>271</v>
       </c>
-      <c r="B122" s="1" t="s">
-        <v>272</v>
-      </c>
       <c r="C122" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D122" s="1" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="E122" s="1" t="s">
         <v>32</v>
@@ -4829,16 +4826,16 @@
     </row>
     <row r="123" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A123" s="1" t="s">
+        <v>272</v>
+      </c>
+      <c r="B123" s="1" t="s">
         <v>273</v>
       </c>
-      <c r="B123" s="1" t="s">
-        <v>274</v>
-      </c>
       <c r="C123" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D123" s="1" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="E123" s="1" t="s">
         <v>35</v>
@@ -4849,16 +4846,16 @@
     </row>
     <row r="124" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A124" s="1" t="s">
+        <v>274</v>
+      </c>
+      <c r="B124" s="1" t="s">
         <v>275</v>
       </c>
-      <c r="B124" s="1" t="s">
-        <v>276</v>
-      </c>
       <c r="C124" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D124" s="1" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="E124" s="1" t="s">
         <v>38</v>
@@ -4869,16 +4866,16 @@
     </row>
     <row r="125" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A125" s="1" t="s">
+        <v>276</v>
+      </c>
+      <c r="B125" s="1" t="s">
         <v>277</v>
       </c>
-      <c r="B125" s="1" t="s">
-        <v>278</v>
-      </c>
       <c r="C125" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D125" s="1" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="E125" s="1" t="s">
         <v>58</v>
@@ -4889,19 +4886,19 @@
     </row>
     <row r="126" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A126" s="1" t="s">
+        <v>278</v>
+      </c>
+      <c r="B126" s="1" t="s">
         <v>279</v>
       </c>
-      <c r="B126" s="1" t="s">
-        <v>280</v>
-      </c>
       <c r="C126" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D126" s="1" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="E126" s="1" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="F126" s="1" t="s">
         <v>105</v>
@@ -4909,16 +4906,16 @@
     </row>
     <row r="127" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A127" s="1" t="s">
+        <v>280</v>
+      </c>
+      <c r="B127" s="1" t="s">
         <v>281</v>
       </c>
-      <c r="B127" s="1" t="s">
+      <c r="C127" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D127" s="1" t="s">
         <v>282</v>
-      </c>
-      <c r="C127" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D127" s="1" t="s">
-        <v>283</v>
       </c>
       <c r="E127" s="1" t="s">
         <v>4</v>
@@ -4929,16 +4926,16 @@
     </row>
     <row r="128" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A128" s="1" t="s">
+        <v>283</v>
+      </c>
+      <c r="B128" s="1" t="s">
         <v>284</v>
       </c>
-      <c r="B128" s="1" t="s">
-        <v>285</v>
-      </c>
       <c r="C128" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D128" s="1" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="E128" s="1" t="s">
         <v>8</v>
@@ -4949,16 +4946,16 @@
     </row>
     <row r="129" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A129" s="1" t="s">
+        <v>285</v>
+      </c>
+      <c r="B129" s="1" t="s">
         <v>286</v>
       </c>
-      <c r="B129" s="1" t="s">
-        <v>287</v>
-      </c>
       <c r="C129" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D129" s="1" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="E129" s="1" t="s">
         <v>11</v>
@@ -4969,16 +4966,16 @@
     </row>
     <row r="130" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A130" s="1" t="s">
+        <v>287</v>
+      </c>
+      <c r="B130" s="1" t="s">
         <v>288</v>
       </c>
-      <c r="B130" s="1" t="s">
-        <v>289</v>
-      </c>
       <c r="C130" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D130" s="1" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="E130" s="1" t="s">
         <v>14</v>
@@ -4989,16 +4986,16 @@
     </row>
     <row r="131" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A131" s="1" t="s">
+        <v>289</v>
+      </c>
+      <c r="B131" s="1" t="s">
         <v>290</v>
       </c>
-      <c r="B131" s="1" t="s">
-        <v>291</v>
-      </c>
       <c r="C131" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D131" s="1" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="E131" s="1" t="s">
         <v>18</v>
@@ -5009,16 +5006,16 @@
     </row>
     <row r="132" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A132" s="1" t="s">
+        <v>291</v>
+      </c>
+      <c r="B132" s="1" t="s">
         <v>292</v>
       </c>
-      <c r="B132" s="1" t="s">
-        <v>293</v>
-      </c>
       <c r="C132" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D132" s="1" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="E132" s="1" t="s">
         <v>32</v>
@@ -5029,16 +5026,16 @@
     </row>
     <row r="133" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A133" s="1" t="s">
+        <v>293</v>
+      </c>
+      <c r="B133" s="1" t="s">
         <v>294</v>
       </c>
-      <c r="B133" s="1" t="s">
-        <v>295</v>
-      </c>
       <c r="C133" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D133" s="1" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="E133" s="1" t="s">
         <v>35</v>
@@ -5049,16 +5046,16 @@
     </row>
     <row r="134" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A134" s="1" t="s">
+        <v>295</v>
+      </c>
+      <c r="B134" s="1" t="s">
         <v>296</v>
       </c>
-      <c r="B134" s="1" t="s">
-        <v>297</v>
-      </c>
       <c r="C134" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D134" s="1" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="E134" s="1" t="s">
         <v>38</v>
@@ -5069,16 +5066,16 @@
     </row>
     <row r="135" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A135" s="1" t="s">
+        <v>297</v>
+      </c>
+      <c r="B135" s="1" t="s">
         <v>298</v>
       </c>
-      <c r="B135" s="1" t="s">
+      <c r="C135" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D135" s="1" t="s">
         <v>299</v>
-      </c>
-      <c r="C135" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D135" s="1" t="s">
-        <v>300</v>
       </c>
       <c r="E135" s="1" t="s">
         <v>4</v>
@@ -5089,16 +5086,16 @@
     </row>
     <row r="136" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A136" s="1" t="s">
+        <v>300</v>
+      </c>
+      <c r="B136" s="1" t="s">
         <v>301</v>
       </c>
-      <c r="B136" s="1" t="s">
-        <v>302</v>
-      </c>
       <c r="C136" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D136" s="1" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="E136" s="1" t="s">
         <v>8</v>
@@ -5109,16 +5106,16 @@
     </row>
     <row r="137" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A137" s="1" t="s">
+        <v>302</v>
+      </c>
+      <c r="B137" s="1" t="s">
         <v>303</v>
       </c>
-      <c r="B137" s="1" t="s">
-        <v>304</v>
-      </c>
       <c r="C137" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D137" s="1" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="E137" s="1" t="s">
         <v>11</v>
@@ -5129,16 +5126,16 @@
     </row>
     <row r="138" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A138" s="1" t="s">
+        <v>304</v>
+      </c>
+      <c r="B138" s="1" t="s">
         <v>305</v>
       </c>
-      <c r="B138" s="1" t="s">
-        <v>306</v>
-      </c>
       <c r="C138" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D138" s="1" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="E138" s="1" t="s">
         <v>14</v>
@@ -5149,56 +5146,56 @@
     </row>
     <row r="139" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A139" s="1" t="s">
+        <v>306</v>
+      </c>
+      <c r="B139" s="1" t="s">
         <v>307</v>
       </c>
-      <c r="B139" s="1" t="s">
-        <v>308</v>
-      </c>
       <c r="C139" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D139" s="1" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="E139" s="1" t="s">
         <v>18</v>
       </c>
       <c r="F139" s="1" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
     </row>
     <row r="140" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A140" s="1" t="s">
+        <v>309</v>
+      </c>
+      <c r="B140" s="1" t="s">
         <v>310</v>
       </c>
-      <c r="B140" s="1" t="s">
-        <v>311</v>
-      </c>
       <c r="C140" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D140" s="1" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="E140" s="1" t="s">
         <v>32</v>
       </c>
       <c r="F140" s="1" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
     </row>
     <row r="141" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A141" s="1" t="s">
+        <v>311</v>
+      </c>
+      <c r="B141" s="1" t="s">
         <v>312</v>
       </c>
-      <c r="B141" s="1" t="s">
-        <v>313</v>
-      </c>
       <c r="C141" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D141" s="1" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="E141" s="1" t="s">
         <v>35</v>
@@ -5209,16 +5206,16 @@
     </row>
     <row r="142" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A142" s="1" t="s">
+        <v>313</v>
+      </c>
+      <c r="B142" s="1" t="s">
         <v>314</v>
       </c>
-      <c r="B142" s="1" t="s">
-        <v>315</v>
-      </c>
       <c r="C142" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D142" s="1" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="E142" s="1" t="s">
         <v>38</v>
@@ -5229,16 +5226,16 @@
     </row>
     <row r="143" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A143" s="1" t="s">
+        <v>315</v>
+      </c>
+      <c r="B143" s="1" t="s">
         <v>316</v>
       </c>
-      <c r="B143" s="1" t="s">
-        <v>317</v>
-      </c>
       <c r="C143" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D143" s="1" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="E143" s="1" t="s">
         <v>58</v>
@@ -5249,16 +5246,16 @@
     </row>
     <row r="144" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A144" s="1" t="s">
+        <v>317</v>
+      </c>
+      <c r="B144" s="1" t="s">
         <v>318</v>
       </c>
-      <c r="B144" s="1" t="s">
+      <c r="C144" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D144" s="1" t="s">
         <v>319</v>
-      </c>
-      <c r="C144" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D144" s="1" t="s">
-        <v>320</v>
       </c>
       <c r="E144" s="1" t="s">
         <v>4</v>
@@ -5269,16 +5266,16 @@
     </row>
     <row r="145" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A145" s="1" t="s">
+        <v>320</v>
+      </c>
+      <c r="B145" s="1" t="s">
         <v>321</v>
       </c>
-      <c r="B145" s="1" t="s">
-        <v>322</v>
-      </c>
       <c r="C145" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D145" s="1" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="E145" s="1" t="s">
         <v>8</v>
@@ -5289,76 +5286,76 @@
     </row>
     <row r="146" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A146" s="1" t="s">
+        <v>322</v>
+      </c>
+      <c r="B146" s="1" t="s">
         <v>323</v>
       </c>
-      <c r="B146" s="1" t="s">
-        <v>324</v>
-      </c>
       <c r="C146" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D146" s="1" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="E146" s="1" t="s">
         <v>11</v>
       </c>
       <c r="F146" s="1" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
     </row>
     <row r="147" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A147" s="1" t="s">
+        <v>325</v>
+      </c>
+      <c r="B147" s="1" t="s">
         <v>326</v>
       </c>
-      <c r="B147" s="1" t="s">
-        <v>327</v>
-      </c>
       <c r="C147" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D147" s="1" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="E147" s="1" t="s">
         <v>14</v>
       </c>
       <c r="F147" s="1" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
     </row>
     <row r="148" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A148" s="1" t="s">
+        <v>327</v>
+      </c>
+      <c r="B148" s="1" t="s">
         <v>328</v>
       </c>
-      <c r="B148" s="1" t="s">
-        <v>329</v>
-      </c>
       <c r="C148" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D148" s="1" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="E148" s="1" t="s">
         <v>18</v>
       </c>
       <c r="F148" s="1" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
     </row>
     <row r="149" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A149" s="1" t="s">
+        <v>329</v>
+      </c>
+      <c r="B149" s="1" t="s">
         <v>330</v>
       </c>
-      <c r="B149" s="1" t="s">
-        <v>331</v>
-      </c>
       <c r="C149" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D149" s="1" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="E149" s="1" t="s">
         <v>32</v>
@@ -5369,16 +5366,16 @@
     </row>
     <row r="150" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A150" s="1" t="s">
+        <v>331</v>
+      </c>
+      <c r="B150" s="1" t="s">
         <v>332</v>
       </c>
-      <c r="B150" s="1" t="s">
-        <v>333</v>
-      </c>
       <c r="C150" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D150" s="1" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="E150" s="1" t="s">
         <v>35</v>
@@ -5389,16 +5386,16 @@
     </row>
     <row r="151" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A151" s="1" t="s">
+        <v>333</v>
+      </c>
+      <c r="B151" s="1" t="s">
         <v>334</v>
       </c>
-      <c r="B151" s="1" t="s">
-        <v>335</v>
-      </c>
       <c r="C151" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D151" s="1" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="E151" s="1" t="s">
         <v>38</v>
@@ -5409,16 +5406,16 @@
     </row>
     <row r="152" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A152" s="1" t="s">
+        <v>335</v>
+      </c>
+      <c r="B152" s="1" t="s">
         <v>336</v>
       </c>
-      <c r="B152" s="1" t="s">
+      <c r="C152" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D152" s="1" t="s">
         <v>337</v>
-      </c>
-      <c r="C152" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D152" s="1" t="s">
-        <v>338</v>
       </c>
       <c r="E152" s="1" t="s">
         <v>4</v>
@@ -5429,16 +5426,16 @@
     </row>
     <row r="153" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A153" s="1" t="s">
+        <v>338</v>
+      </c>
+      <c r="B153" s="1" t="s">
         <v>339</v>
       </c>
-      <c r="B153" s="1" t="s">
-        <v>340</v>
-      </c>
       <c r="C153" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D153" s="1" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="E153" s="1" t="s">
         <v>8</v>
@@ -5449,16 +5446,16 @@
     </row>
     <row r="154" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A154" s="1" t="s">
+        <v>340</v>
+      </c>
+      <c r="B154" s="1" t="s">
         <v>341</v>
       </c>
-      <c r="B154" s="1" t="s">
-        <v>342</v>
-      </c>
       <c r="C154" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D154" s="1" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="E154" s="1" t="s">
         <v>11</v>
@@ -5469,16 +5466,16 @@
     </row>
     <row r="155" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A155" s="1" t="s">
+        <v>342</v>
+      </c>
+      <c r="B155" s="1" t="s">
         <v>343</v>
       </c>
-      <c r="B155" s="1" t="s">
-        <v>344</v>
-      </c>
       <c r="C155" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D155" s="1" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="E155" s="1" t="s">
         <v>14</v>
@@ -5489,16 +5486,16 @@
     </row>
     <row r="156" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A156" s="1" t="s">
+        <v>344</v>
+      </c>
+      <c r="B156" s="1" t="s">
         <v>345</v>
       </c>
-      <c r="B156" s="1" t="s">
-        <v>346</v>
-      </c>
       <c r="C156" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D156" s="1" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="E156" s="1" t="s">
         <v>18</v>
@@ -5509,16 +5506,16 @@
     </row>
     <row r="157" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A157" s="1" t="s">
+        <v>346</v>
+      </c>
+      <c r="B157" s="1" t="s">
         <v>347</v>
       </c>
-      <c r="B157" s="1" t="s">
-        <v>348</v>
-      </c>
       <c r="C157" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D157" s="1" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="E157" s="1" t="s">
         <v>32</v>
@@ -5529,16 +5526,16 @@
     </row>
     <row r="158" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A158" s="1" t="s">
+        <v>348</v>
+      </c>
+      <c r="B158" s="1" t="s">
         <v>349</v>
       </c>
-      <c r="B158" s="1" t="s">
-        <v>350</v>
-      </c>
       <c r="C158" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D158" s="1" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="E158" s="1" t="s">
         <v>35</v>
@@ -5549,16 +5546,16 @@
     </row>
     <row r="159" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A159" s="1" t="s">
+        <v>350</v>
+      </c>
+      <c r="B159" s="1" t="s">
         <v>351</v>
       </c>
-      <c r="B159" s="1" t="s">
-        <v>352</v>
-      </c>
       <c r="C159" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D159" s="1" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="E159" s="1" t="s">
         <v>38</v>
@@ -5569,56 +5566,56 @@
     </row>
     <row r="160" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A160" s="1" t="s">
+        <v>352</v>
+      </c>
+      <c r="B160" s="1" t="s">
         <v>353</v>
       </c>
-      <c r="B160" s="1" t="s">
+      <c r="C160" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D160" s="1" t="s">
         <v>354</v>
-      </c>
-      <c r="C160" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D160" s="1" t="s">
-        <v>355</v>
       </c>
       <c r="E160" s="1" t="s">
         <v>4</v>
       </c>
       <c r="F160" s="1" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
     </row>
     <row r="161" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A161" s="1" t="s">
+        <v>356</v>
+      </c>
+      <c r="B161" s="1" t="s">
         <v>357</v>
       </c>
-      <c r="B161" s="1" t="s">
-        <v>358</v>
-      </c>
       <c r="C161" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D161" s="1" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="E161" s="1" t="s">
         <v>8</v>
       </c>
       <c r="F161" s="1" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
     </row>
     <row r="162" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A162" s="1" t="s">
+        <v>358</v>
+      </c>
+      <c r="B162" s="1" t="s">
         <v>359</v>
       </c>
-      <c r="B162" s="1" t="s">
-        <v>360</v>
-      </c>
       <c r="C162" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D162" s="1" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="E162" s="1" t="s">
         <v>11</v>
@@ -5629,16 +5626,16 @@
     </row>
     <row r="163" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A163" s="1" t="s">
+        <v>360</v>
+      </c>
+      <c r="B163" s="1" t="s">
         <v>361</v>
       </c>
-      <c r="B163" s="1" t="s">
-        <v>362</v>
-      </c>
       <c r="C163" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D163" s="1" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="E163" s="1" t="s">
         <v>14</v>
@@ -5649,16 +5646,16 @@
     </row>
     <row r="164" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A164" s="1" t="s">
+        <v>362</v>
+      </c>
+      <c r="B164" s="1" t="s">
         <v>363</v>
       </c>
-      <c r="B164" s="1" t="s">
-        <v>364</v>
-      </c>
       <c r="C164" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D164" s="1" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="E164" s="1" t="s">
         <v>18</v>
@@ -5669,16 +5666,16 @@
     </row>
     <row r="165" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A165" s="1" t="s">
+        <v>364</v>
+      </c>
+      <c r="B165" s="1" t="s">
         <v>365</v>
       </c>
-      <c r="B165" s="1" t="s">
-        <v>366</v>
-      </c>
       <c r="C165" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D165" s="1" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="E165" s="1" t="s">
         <v>32</v>
@@ -5689,16 +5686,16 @@
     </row>
     <row r="166" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A166" s="1" t="s">
+        <v>366</v>
+      </c>
+      <c r="B166" s="1" t="s">
         <v>367</v>
       </c>
-      <c r="B166" s="1" t="s">
-        <v>368</v>
-      </c>
       <c r="C166" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D166" s="1" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="E166" s="1" t="s">
         <v>35</v>
@@ -5709,16 +5706,16 @@
     </row>
     <row r="167" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A167" s="1" t="s">
+        <v>368</v>
+      </c>
+      <c r="B167" s="1" t="s">
         <v>369</v>
       </c>
-      <c r="B167" s="1" t="s">
-        <v>370</v>
-      </c>
       <c r="C167" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D167" s="1" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="E167" s="1" t="s">
         <v>38</v>
@@ -5729,16 +5726,16 @@
     </row>
     <row r="168" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A168" s="1" t="s">
+        <v>370</v>
+      </c>
+      <c r="B168" s="1" t="s">
         <v>371</v>
       </c>
-      <c r="B168" s="1" t="s">
-        <v>372</v>
-      </c>
       <c r="C168" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D168" s="1" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="E168" s="1" t="s">
         <v>58</v>
@@ -5749,16 +5746,16 @@
     </row>
     <row r="169" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A169" s="1" t="s">
+        <v>372</v>
+      </c>
+      <c r="B169" s="1" t="s">
         <v>373</v>
       </c>
-      <c r="B169" s="1" t="s">
+      <c r="C169" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D169" s="1" t="s">
         <v>374</v>
-      </c>
-      <c r="C169" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D169" s="1" t="s">
-        <v>375</v>
       </c>
       <c r="E169" s="1" t="s">
         <v>4</v>
@@ -5769,16 +5766,16 @@
     </row>
     <row r="170" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A170" s="1" t="s">
+        <v>375</v>
+      </c>
+      <c r="B170" s="1" t="s">
         <v>376</v>
       </c>
-      <c r="B170" s="1" t="s">
-        <v>377</v>
-      </c>
       <c r="C170" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D170" s="1" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="E170" s="1" t="s">
         <v>8</v>
@@ -5789,16 +5786,16 @@
     </row>
     <row r="171" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A171" s="1" t="s">
+        <v>377</v>
+      </c>
+      <c r="B171" s="1" t="s">
         <v>378</v>
       </c>
-      <c r="B171" s="1" t="s">
-        <v>379</v>
-      </c>
       <c r="C171" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D171" s="1" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="E171" s="1" t="s">
         <v>11</v>
@@ -5809,16 +5806,16 @@
     </row>
     <row r="172" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A172" s="1" t="s">
+        <v>379</v>
+      </c>
+      <c r="B172" s="1" t="s">
         <v>380</v>
       </c>
-      <c r="B172" s="1" t="s">
-        <v>381</v>
-      </c>
       <c r="C172" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D172" s="1" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="E172" s="1" t="s">
         <v>14</v>
@@ -5829,16 +5826,16 @@
     </row>
     <row r="173" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A173" s="1" t="s">
+        <v>381</v>
+      </c>
+      <c r="B173" s="1" t="s">
         <v>382</v>
       </c>
-      <c r="B173" s="1" t="s">
-        <v>383</v>
-      </c>
       <c r="C173" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D173" s="1" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="E173" s="1" t="s">
         <v>18</v>
@@ -5849,16 +5846,16 @@
     </row>
     <row r="174" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A174" s="1" t="s">
+        <v>383</v>
+      </c>
+      <c r="B174" s="1" t="s">
         <v>384</v>
       </c>
-      <c r="B174" s="1" t="s">
-        <v>385</v>
-      </c>
       <c r="C174" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D174" s="1" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="E174" s="1" t="s">
         <v>32</v>
@@ -5869,16 +5866,16 @@
     </row>
     <row r="175" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A175" s="1" t="s">
+        <v>385</v>
+      </c>
+      <c r="B175" s="1" t="s">
         <v>386</v>
       </c>
-      <c r="B175" s="1" t="s">
-        <v>387</v>
-      </c>
       <c r="C175" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D175" s="1" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="E175" s="1" t="s">
         <v>35</v>
@@ -5889,16 +5886,16 @@
     </row>
     <row r="176" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A176" s="1" t="s">
+        <v>387</v>
+      </c>
+      <c r="B176" s="1" t="s">
         <v>388</v>
       </c>
-      <c r="B176" s="1" t="s">
-        <v>389</v>
-      </c>
       <c r="C176" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D176" s="1" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="E176" s="1" t="s">
         <v>38</v>
@@ -5909,16 +5906,16 @@
     </row>
     <row r="177" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A177" s="1" t="s">
+        <v>389</v>
+      </c>
+      <c r="B177" s="1" t="s">
         <v>390</v>
       </c>
-      <c r="B177" s="1" t="s">
+      <c r="C177" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D177" s="1" t="s">
         <v>391</v>
-      </c>
-      <c r="C177" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D177" s="1" t="s">
-        <v>392</v>
       </c>
       <c r="E177" s="1" t="s">
         <v>4</v>
@@ -5929,16 +5926,16 @@
     </row>
     <row r="178" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A178" s="1" t="s">
+        <v>392</v>
+      </c>
+      <c r="B178" s="1" t="s">
         <v>393</v>
       </c>
-      <c r="B178" s="1" t="s">
-        <v>394</v>
-      </c>
       <c r="C178" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D178" s="1" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="E178" s="1" t="s">
         <v>8</v>
@@ -5949,16 +5946,16 @@
     </row>
     <row r="179" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A179" s="1" t="s">
+        <v>394</v>
+      </c>
+      <c r="B179" s="1" t="s">
         <v>395</v>
       </c>
-      <c r="B179" s="1" t="s">
-        <v>396</v>
-      </c>
       <c r="C179" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D179" s="1" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="E179" s="1" t="s">
         <v>11</v>
@@ -5969,16 +5966,16 @@
     </row>
     <row r="180" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A180" s="1" t="s">
+        <v>396</v>
+      </c>
+      <c r="B180" s="1" t="s">
         <v>397</v>
       </c>
-      <c r="B180" s="1" t="s">
-        <v>398</v>
-      </c>
       <c r="C180" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D180" s="1" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="E180" s="1" t="s">
         <v>14</v>
@@ -5989,16 +5986,16 @@
     </row>
     <row r="181" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A181" s="1" t="s">
+        <v>398</v>
+      </c>
+      <c r="B181" s="1" t="s">
         <v>399</v>
       </c>
-      <c r="B181" s="1" t="s">
-        <v>400</v>
-      </c>
       <c r="C181" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D181" s="1" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="E181" s="1" t="s">
         <v>18</v>
@@ -6009,16 +6006,16 @@
     </row>
     <row r="182" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A182" s="1" t="s">
+        <v>400</v>
+      </c>
+      <c r="B182" s="1" t="s">
         <v>401</v>
       </c>
-      <c r="B182" s="1" t="s">
-        <v>402</v>
-      </c>
       <c r="C182" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D182" s="1" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="E182" s="1" t="s">
         <v>32</v>
@@ -6029,16 +6026,16 @@
     </row>
     <row r="183" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A183" s="1" t="s">
+        <v>402</v>
+      </c>
+      <c r="B183" s="1" t="s">
         <v>403</v>
       </c>
-      <c r="B183" s="1" t="s">
-        <v>404</v>
-      </c>
       <c r="C183" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D183" s="1" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="E183" s="1" t="s">
         <v>35</v>
@@ -6049,16 +6046,16 @@
     </row>
     <row r="184" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A184" s="1" t="s">
+        <v>404</v>
+      </c>
+      <c r="B184" s="1" t="s">
         <v>405</v>
       </c>
-      <c r="B184" s="1" t="s">
+      <c r="C184" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D184" s="1" t="s">
         <v>406</v>
-      </c>
-      <c r="C184" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D184" s="1" t="s">
-        <v>407</v>
       </c>
       <c r="E184" s="1" t="s">
         <v>4</v>
@@ -6069,16 +6066,16 @@
     </row>
     <row r="185" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A185" s="1" t="s">
+        <v>407</v>
+      </c>
+      <c r="B185" s="1" t="s">
         <v>408</v>
       </c>
-      <c r="B185" s="1" t="s">
-        <v>409</v>
-      </c>
       <c r="C185" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D185" s="1" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="E185" s="1" t="s">
         <v>8</v>
@@ -6089,16 +6086,16 @@
     </row>
     <row r="186" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A186" s="1" t="s">
+        <v>409</v>
+      </c>
+      <c r="B186" s="1" t="s">
         <v>410</v>
       </c>
-      <c r="B186" s="1" t="s">
-        <v>411</v>
-      </c>
       <c r="C186" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D186" s="1" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="E186" s="1" t="s">
         <v>11</v>
@@ -6109,16 +6106,16 @@
     </row>
     <row r="187" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A187" s="1" t="s">
+        <v>411</v>
+      </c>
+      <c r="B187" s="1" t="s">
         <v>412</v>
       </c>
-      <c r="B187" s="1" t="s">
-        <v>413</v>
-      </c>
       <c r="C187" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D187" s="1" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="E187" s="1" t="s">
         <v>14</v>
@@ -6129,16 +6126,16 @@
     </row>
     <row r="188" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A188" s="1" t="s">
+        <v>413</v>
+      </c>
+      <c r="B188" s="1" t="s">
         <v>414</v>
       </c>
-      <c r="B188" s="1" t="s">
-        <v>415</v>
-      </c>
       <c r="C188" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D188" s="1" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="E188" s="1" t="s">
         <v>18</v>
@@ -6149,16 +6146,16 @@
     </row>
     <row r="189" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A189" s="1" t="s">
+        <v>415</v>
+      </c>
+      <c r="B189" s="1" t="s">
         <v>416</v>
       </c>
-      <c r="B189" s="1" t="s">
-        <v>417</v>
-      </c>
       <c r="C189" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D189" s="1" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="E189" s="1" t="s">
         <v>32</v>
@@ -6169,16 +6166,16 @@
     </row>
     <row r="190" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A190" s="1" t="s">
+        <v>417</v>
+      </c>
+      <c r="B190" s="1" t="s">
         <v>418</v>
       </c>
-      <c r="B190" s="1" t="s">
-        <v>419</v>
-      </c>
       <c r="C190" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D190" s="1" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="E190" s="1" t="s">
         <v>35</v>
@@ -6189,16 +6186,16 @@
     </row>
     <row r="191" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A191" s="1" t="s">
+        <v>419</v>
+      </c>
+      <c r="B191" s="1" t="s">
         <v>420</v>
       </c>
-      <c r="B191" s="1" t="s">
-        <v>421</v>
-      </c>
       <c r="C191" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D191" s="1" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="E191" s="1" t="s">
         <v>38</v>
@@ -6209,16 +6206,16 @@
     </row>
     <row r="192" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A192" s="1" t="s">
+        <v>421</v>
+      </c>
+      <c r="B192" s="1" t="s">
         <v>422</v>
       </c>
-      <c r="B192" s="1" t="s">
+      <c r="C192" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D192" s="1" t="s">
         <v>423</v>
-      </c>
-      <c r="C192" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D192" s="1" t="s">
-        <v>424</v>
       </c>
       <c r="E192" s="1" t="s">
         <v>4</v>
@@ -6229,36 +6226,36 @@
     </row>
     <row r="193" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A193" s="1" t="s">
+        <v>424</v>
+      </c>
+      <c r="B193" s="1" t="s">
         <v>425</v>
       </c>
-      <c r="B193" s="1" t="s">
-        <v>426</v>
-      </c>
       <c r="C193" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D193" s="1" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="E193" s="1" t="s">
         <v>8</v>
       </c>
       <c r="F193" s="1" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
     </row>
     <row r="194" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A194" s="1" t="s">
+        <v>426</v>
+      </c>
+      <c r="B194" s="1" t="s">
         <v>427</v>
       </c>
-      <c r="B194" s="1" t="s">
-        <v>428</v>
-      </c>
       <c r="C194" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D194" s="1" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="E194" s="1" t="s">
         <v>11</v>
@@ -6269,16 +6266,16 @@
     </row>
     <row r="195" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A195" s="1" t="s">
+        <v>428</v>
+      </c>
+      <c r="B195" s="1" t="s">
         <v>429</v>
       </c>
-      <c r="B195" s="1" t="s">
-        <v>430</v>
-      </c>
       <c r="C195" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D195" s="1" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="E195" s="1" t="s">
         <v>14</v>
@@ -6289,16 +6286,16 @@
     </row>
     <row r="196" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A196" s="1" t="s">
+        <v>430</v>
+      </c>
+      <c r="B196" s="1" t="s">
         <v>431</v>
       </c>
-      <c r="B196" s="1" t="s">
-        <v>432</v>
-      </c>
       <c r="C196" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D196" s="1" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="E196" s="1" t="s">
         <v>18</v>
@@ -6309,16 +6306,16 @@
     </row>
     <row r="197" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A197" s="1" t="s">
+        <v>432</v>
+      </c>
+      <c r="B197" s="1" t="s">
         <v>433</v>
       </c>
-      <c r="B197" s="1" t="s">
-        <v>434</v>
-      </c>
       <c r="C197" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D197" s="1" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="E197" s="1" t="s">
         <v>32</v>
@@ -6329,16 +6326,16 @@
     </row>
     <row r="198" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A198" s="1" t="s">
+        <v>434</v>
+      </c>
+      <c r="B198" s="1" t="s">
         <v>435</v>
       </c>
-      <c r="B198" s="1" t="s">
-        <v>436</v>
-      </c>
       <c r="C198" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D198" s="1" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="E198" s="1" t="s">
         <v>35</v>
@@ -6349,16 +6346,16 @@
     </row>
     <row r="199" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A199" s="1" t="s">
+        <v>436</v>
+      </c>
+      <c r="B199" s="1" t="s">
         <v>437</v>
       </c>
-      <c r="B199" s="1" t="s">
+      <c r="C199" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D199" s="1" t="s">
         <v>438</v>
-      </c>
-      <c r="C199" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D199" s="1" t="s">
-        <v>439</v>
       </c>
       <c r="E199" s="1" t="s">
         <v>4</v>
@@ -6369,16 +6366,16 @@
     </row>
     <row r="200" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A200" s="1" t="s">
+        <v>439</v>
+      </c>
+      <c r="B200" s="1" t="s">
         <v>440</v>
       </c>
-      <c r="B200" s="1" t="s">
-        <v>441</v>
-      </c>
       <c r="C200" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D200" s="1" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="E200" s="1" t="s">
         <v>8</v>
@@ -6389,16 +6386,16 @@
     </row>
     <row r="201" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A201" s="1" t="s">
+        <v>441</v>
+      </c>
+      <c r="B201" s="1" t="s">
         <v>442</v>
       </c>
-      <c r="B201" s="1" t="s">
-        <v>443</v>
-      </c>
       <c r="C201" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D201" s="1" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="E201" s="1" t="s">
         <v>11</v>
@@ -6409,16 +6406,16 @@
     </row>
     <row r="202" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A202" s="1" t="s">
+        <v>443</v>
+      </c>
+      <c r="B202" s="1" t="s">
         <v>444</v>
       </c>
-      <c r="B202" s="1" t="s">
-        <v>445</v>
-      </c>
       <c r="C202" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D202" s="1" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="E202" s="1" t="s">
         <v>14</v>
@@ -6429,16 +6426,16 @@
     </row>
     <row r="203" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A203" s="1" t="s">
+        <v>445</v>
+      </c>
+      <c r="B203" s="1" t="s">
         <v>446</v>
       </c>
-      <c r="B203" s="1" t="s">
+      <c r="C203" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D203" s="1" t="s">
         <v>447</v>
-      </c>
-      <c r="C203" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D203" s="1" t="s">
-        <v>448</v>
       </c>
       <c r="E203" s="1" t="s">
         <v>4</v>
@@ -6449,16 +6446,16 @@
     </row>
     <row r="204" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A204" s="1" t="s">
+        <v>448</v>
+      </c>
+      <c r="B204" s="1" t="s">
         <v>449</v>
       </c>
-      <c r="B204" s="1" t="s">
-        <v>450</v>
-      </c>
       <c r="C204" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D204" s="1" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="E204" s="1" t="s">
         <v>8</v>
@@ -6469,16 +6466,16 @@
     </row>
     <row r="205" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A205" s="1" t="s">
+        <v>450</v>
+      </c>
+      <c r="B205" s="1" t="s">
         <v>451</v>
       </c>
-      <c r="B205" s="1" t="s">
-        <v>452</v>
-      </c>
       <c r="C205" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D205" s="1" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="E205" s="1" t="s">
         <v>11</v>
@@ -6489,16 +6486,16 @@
     </row>
     <row r="206" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A206" s="1" t="s">
+        <v>452</v>
+      </c>
+      <c r="B206" s="1" t="s">
         <v>453</v>
       </c>
-      <c r="B206" s="1" t="s">
-        <v>454</v>
-      </c>
       <c r="C206" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D206" s="1" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="E206" s="1" t="s">
         <v>14</v>
@@ -6509,16 +6506,16 @@
     </row>
     <row r="207" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A207" s="1" t="s">
+        <v>454</v>
+      </c>
+      <c r="B207" s="1" t="s">
         <v>455</v>
       </c>
-      <c r="B207" s="1" t="s">
-        <v>456</v>
-      </c>
       <c r="C207" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D207" s="1" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="E207" s="1" t="s">
         <v>18</v>
@@ -6529,16 +6526,16 @@
     </row>
     <row r="208" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A208" s="1" t="s">
+        <v>456</v>
+      </c>
+      <c r="B208" s="1" t="s">
         <v>457</v>
       </c>
-      <c r="B208" s="1" t="s">
-        <v>458</v>
-      </c>
       <c r="C208" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D208" s="1" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="E208" s="1" t="s">
         <v>32</v>
@@ -6549,16 +6546,16 @@
     </row>
     <row r="209" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A209" s="1" t="s">
+        <v>458</v>
+      </c>
+      <c r="B209" s="1" t="s">
         <v>459</v>
       </c>
-      <c r="B209" s="1" t="s">
-        <v>460</v>
-      </c>
       <c r="C209" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D209" s="1" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="E209" s="1" t="s">
         <v>35</v>
@@ -6569,56 +6566,56 @@
     </row>
     <row r="210" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A210" s="1" t="s">
+        <v>460</v>
+      </c>
+      <c r="B210" s="1" t="s">
         <v>461</v>
       </c>
-      <c r="B210" s="1" t="s">
-        <v>462</v>
-      </c>
       <c r="C210" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D210" s="1" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="E210" s="1" t="s">
         <v>38</v>
       </c>
       <c r="F210" s="1" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
     </row>
     <row r="211" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A211" s="1" t="s">
+        <v>462</v>
+      </c>
+      <c r="B211" s="1" t="s">
         <v>463</v>
       </c>
-      <c r="B211" s="1" t="s">
-        <v>464</v>
-      </c>
       <c r="C211" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D211" s="1" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="E211" s="1" t="s">
         <v>58</v>
       </c>
       <c r="F211" s="1" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
     </row>
     <row r="212" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A212" s="1" t="s">
+        <v>464</v>
+      </c>
+      <c r="B212" s="1" t="s">
         <v>465</v>
       </c>
-      <c r="B212" s="1" t="s">
+      <c r="C212" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D212" s="1" t="s">
         <v>466</v>
-      </c>
-      <c r="C212" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D212" s="1" t="s">
-        <v>467</v>
       </c>
       <c r="E212" s="1" t="s">
         <v>4</v>
@@ -6629,16 +6626,16 @@
     </row>
     <row r="213" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A213" s="1" t="s">
+        <v>467</v>
+      </c>
+      <c r="B213" s="1" t="s">
         <v>468</v>
       </c>
-      <c r="B213" s="1" t="s">
-        <v>469</v>
-      </c>
       <c r="C213" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D213" s="1" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="E213" s="1" t="s">
         <v>8</v>
@@ -6649,16 +6646,16 @@
     </row>
     <row r="214" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A214" s="1" t="s">
+        <v>469</v>
+      </c>
+      <c r="B214" s="1" t="s">
         <v>470</v>
       </c>
-      <c r="B214" s="1" t="s">
-        <v>471</v>
-      </c>
       <c r="C214" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D214" s="1" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="E214" s="1" t="s">
         <v>11</v>
@@ -6669,16 +6666,16 @@
     </row>
     <row r="215" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A215" s="1" t="s">
+        <v>471</v>
+      </c>
+      <c r="B215" s="1" t="s">
         <v>472</v>
       </c>
-      <c r="B215" s="1" t="s">
-        <v>473</v>
-      </c>
       <c r="C215" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D215" s="1" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="E215" s="1" t="s">
         <v>14</v>
@@ -6689,36 +6686,36 @@
     </row>
     <row r="216" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A216" s="1" t="s">
+        <v>473</v>
+      </c>
+      <c r="B216" s="1" t="s">
         <v>474</v>
       </c>
-      <c r="B216" s="1" t="s">
-        <v>475</v>
-      </c>
       <c r="C216" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D216" s="1" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="E216" s="1" t="s">
         <v>18</v>
       </c>
       <c r="F216" s="1" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
     </row>
     <row r="217" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A217" s="1" t="s">
+        <v>475</v>
+      </c>
+      <c r="B217" s="1" t="s">
         <v>476</v>
       </c>
-      <c r="B217" s="1" t="s">
-        <v>477</v>
-      </c>
       <c r="C217" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D217" s="1" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="E217" s="1" t="s">
         <v>32</v>
@@ -6729,16 +6726,16 @@
     </row>
     <row r="218" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A218" s="1" t="s">
+        <v>477</v>
+      </c>
+      <c r="B218" s="1" t="s">
         <v>478</v>
       </c>
-      <c r="B218" s="1" t="s">
-        <v>479</v>
-      </c>
       <c r="C218" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D218" s="1" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="E218" s="1" t="s">
         <v>35</v>
@@ -6749,279 +6746,279 @@
     </row>
     <row r="219" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A219" s="1" t="s">
+        <v>479</v>
+      </c>
+      <c r="B219" s="1" t="s">
         <v>480</v>
       </c>
-      <c r="B219" s="1" t="s">
-        <v>481</v>
-      </c>
       <c r="C219" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D219" s="1" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="E219" s="1" t="s">
         <v>38</v>
       </c>
       <c r="F219" s="1" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
     </row>
     <row r="220" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A220" s="1" t="s">
+        <v>482</v>
+      </c>
+      <c r="B220" s="1" t="s">
         <v>483</v>
       </c>
-      <c r="B220" s="1" t="s">
-        <v>484</v>
-      </c>
       <c r="C220" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D220" s="1" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="E220" s="1" t="s">
         <v>58</v>
       </c>
       <c r="F220" s="1" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
     </row>
     <row r="221" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A221" s="1" t="s">
+        <v>484</v>
+      </c>
+      <c r="B221" s="1" t="s">
         <v>485</v>
       </c>
-      <c r="B221" s="1" t="s">
-        <v>486</v>
-      </c>
       <c r="C221" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D221" s="1" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="E221" s="1" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="F221" s="1" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
     </row>
     <row r="222" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A222" s="1" t="s">
+        <v>486</v>
+      </c>
+      <c r="B222" s="1" t="s">
         <v>487</v>
       </c>
-      <c r="B222" s="1" t="s">
+      <c r="C222" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D222" s="1" t="s">
         <v>488</v>
-      </c>
-      <c r="C222" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D222" s="1" t="s">
-        <v>489</v>
       </c>
       <c r="E222" s="1" t="s">
         <v>4</v>
       </c>
       <c r="F222" s="1" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
     </row>
     <row r="223" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A223" s="1" t="s">
+        <v>489</v>
+      </c>
+      <c r="B223" s="1" t="s">
         <v>490</v>
       </c>
-      <c r="B223" s="1" t="s">
-        <v>491</v>
-      </c>
       <c r="C223" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D223" s="1" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="E223" s="1" t="s">
         <v>8</v>
       </c>
       <c r="F223" s="1" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
     </row>
     <row r="224" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A224" s="1" t="s">
+        <v>491</v>
+      </c>
+      <c r="B224" s="1" t="s">
         <v>492</v>
       </c>
-      <c r="B224" s="1" t="s">
-        <v>493</v>
-      </c>
       <c r="C224" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D224" s="1" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="E224" s="1" t="s">
         <v>11</v>
       </c>
       <c r="F224" s="1" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
     </row>
     <row r="225" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A225" s="1" t="s">
+        <v>493</v>
+      </c>
+      <c r="B225" s="1" t="s">
         <v>494</v>
       </c>
-      <c r="B225" s="1" t="s">
-        <v>495</v>
-      </c>
       <c r="C225" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D225" s="1" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="E225" s="1" t="s">
         <v>14</v>
       </c>
       <c r="F225" s="1" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
     </row>
     <row r="226" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A226" s="1" t="s">
+        <v>495</v>
+      </c>
+      <c r="B226" s="1" t="s">
         <v>496</v>
       </c>
-      <c r="B226" s="1" t="s">
-        <v>497</v>
-      </c>
       <c r="C226" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D226" s="1" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="E226" s="1" t="s">
         <v>18</v>
       </c>
       <c r="F226" s="1" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
     </row>
     <row r="227" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A227" s="1" t="s">
+        <v>497</v>
+      </c>
+      <c r="B227" s="1" t="s">
         <v>498</v>
       </c>
-      <c r="B227" s="1" t="s">
-        <v>499</v>
-      </c>
       <c r="C227" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D227" s="1" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="E227" s="1" t="s">
         <v>32</v>
       </c>
       <c r="F227" s="1" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
     </row>
     <row r="228" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A228" s="1" t="s">
+        <v>499</v>
+      </c>
+      <c r="B228" s="1" t="s">
         <v>500</v>
       </c>
-      <c r="B228" s="1" t="s">
-        <v>501</v>
-      </c>
       <c r="C228" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D228" s="1" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="E228" s="1" t="s">
         <v>35</v>
       </c>
       <c r="F228" s="1" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
     </row>
     <row r="229" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A229" s="1" t="s">
+        <v>501</v>
+      </c>
+      <c r="B229" s="1" t="s">
         <v>502</v>
       </c>
-      <c r="B229" s="1" t="s">
-        <v>503</v>
-      </c>
       <c r="C229" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D229" s="1" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="E229" s="1" t="s">
         <v>38</v>
       </c>
       <c r="F229" s="1" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
     </row>
     <row r="230" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A230" s="1" t="s">
+        <v>503</v>
+      </c>
+      <c r="B230" s="1" t="s">
         <v>504</v>
       </c>
-      <c r="B230" s="1" t="s">
-        <v>505</v>
-      </c>
       <c r="C230" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D230" s="1" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="E230" s="1" t="s">
         <v>58</v>
       </c>
       <c r="F230" s="1" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
     </row>
     <row r="231" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A231" s="1" t="s">
+        <v>505</v>
+      </c>
+      <c r="B231" s="1" t="s">
         <v>506</v>
       </c>
-      <c r="B231" s="1" t="s">
-        <v>507</v>
-      </c>
       <c r="C231" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D231" s="1" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="E231" s="1" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="F231" s="1" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
     </row>
     <row r="232" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A232" s="1" t="s">
+        <v>507</v>
+      </c>
+      <c r="B232" s="1" t="s">
         <v>508</v>
       </c>
-      <c r="B232" s="1" t="s">
-        <v>509</v>
-      </c>
       <c r="C232" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D232" s="1" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="E232" s="1" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="F232" s="1" t="s">
         <v>79</v>
@@ -7029,19 +7026,19 @@
     </row>
     <row r="233" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A233" s="1" t="s">
+        <v>509</v>
+      </c>
+      <c r="B233" s="1" t="s">
         <v>510</v>
       </c>
-      <c r="B233" s="1" t="s">
-        <v>511</v>
-      </c>
       <c r="C233" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D233" s="1" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="E233" s="1" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="F233" s="1" t="s">
         <v>105</v>
@@ -7049,39 +7046,39 @@
     </row>
     <row r="234" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A234" s="1" t="s">
+        <v>511</v>
+      </c>
+      <c r="B234" s="1" t="s">
         <v>512</v>
       </c>
-      <c r="B234" s="1" t="s">
-        <v>513</v>
-      </c>
       <c r="C234" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D234" s="1" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="E234" s="1" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="F234" s="1" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
     </row>
     <row r="235" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A235" s="1" t="s">
+        <v>513</v>
+      </c>
+      <c r="B235" s="1" t="s">
         <v>514</v>
       </c>
-      <c r="B235" s="1" t="s">
-        <v>515</v>
-      </c>
       <c r="C235" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D235" s="1" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="E235" s="1" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="F235" s="1" t="s">
         <v>105</v>
@@ -7089,16 +7086,16 @@
     </row>
     <row r="236" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A236" s="1" t="s">
+        <v>515</v>
+      </c>
+      <c r="B236" s="1" t="s">
         <v>516</v>
       </c>
-      <c r="B236" s="1" t="s">
+      <c r="C236" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D236" s="1" t="s">
         <v>517</v>
-      </c>
-      <c r="C236" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D236" s="1" t="s">
-        <v>518</v>
       </c>
       <c r="E236" s="1" t="s">
         <v>4</v>
@@ -7109,116 +7106,116 @@
     </row>
     <row r="237" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A237" s="1" t="s">
+        <v>518</v>
+      </c>
+      <c r="B237" s="1" t="s">
         <v>519</v>
       </c>
-      <c r="B237" s="1" t="s">
-        <v>520</v>
-      </c>
       <c r="C237" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D237" s="1" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="E237" s="1" t="s">
         <v>8</v>
       </c>
       <c r="F237" s="1" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
     </row>
     <row r="238" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A238" s="1" t="s">
+        <v>520</v>
+      </c>
+      <c r="B238" s="1" t="s">
         <v>521</v>
       </c>
-      <c r="B238" s="1" t="s">
-        <v>522</v>
-      </c>
       <c r="C238" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D238" s="1" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="E238" s="1" t="s">
         <v>11</v>
       </c>
       <c r="F238" s="1" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
     </row>
     <row r="239" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A239" s="1" t="s">
+        <v>522</v>
+      </c>
+      <c r="B239" s="1" t="s">
         <v>523</v>
       </c>
-      <c r="B239" s="1" t="s">
-        <v>524</v>
-      </c>
       <c r="C239" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D239" s="1" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="E239" s="1" t="s">
         <v>14</v>
       </c>
       <c r="F239" s="1" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
     </row>
     <row r="240" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A240" s="1" t="s">
+        <v>524</v>
+      </c>
+      <c r="B240" s="1" t="s">
         <v>525</v>
       </c>
-      <c r="B240" s="1" t="s">
-        <v>526</v>
-      </c>
       <c r="C240" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D240" s="1" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="E240" s="1" t="s">
         <v>18</v>
       </c>
       <c r="F240" s="1" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
     </row>
     <row r="241" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A241" s="1" t="s">
+        <v>526</v>
+      </c>
+      <c r="B241" s="1" t="s">
         <v>527</v>
       </c>
-      <c r="B241" s="1" t="s">
-        <v>528</v>
-      </c>
       <c r="C241" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D241" s="1" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="E241" s="1" t="s">
         <v>32</v>
       </c>
       <c r="F241" s="1" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
     </row>
     <row r="242" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A242" s="1" t="s">
+        <v>528</v>
+      </c>
+      <c r="B242" s="1" t="s">
         <v>529</v>
       </c>
-      <c r="B242" s="1" t="s">
-        <v>530</v>
-      </c>
       <c r="C242" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D242" s="1" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="E242" s="1" t="s">
         <v>35</v>
@@ -7229,16 +7226,16 @@
     </row>
     <row r="243" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A243" s="1" t="s">
+        <v>530</v>
+      </c>
+      <c r="B243" s="1" t="s">
         <v>531</v>
       </c>
-      <c r="B243" s="1" t="s">
-        <v>532</v>
-      </c>
       <c r="C243" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D243" s="1" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="E243" s="1" t="s">
         <v>38</v>
@@ -7249,16 +7246,16 @@
     </row>
     <row r="244" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A244" s="1" t="s">
+        <v>532</v>
+      </c>
+      <c r="B244" s="1" t="s">
         <v>533</v>
       </c>
-      <c r="B244" s="1" t="s">
-        <v>534</v>
-      </c>
       <c r="C244" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D244" s="1" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="E244" s="1" t="s">
         <v>58</v>
@@ -7269,19 +7266,19 @@
     </row>
     <row r="245" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A245" s="1" t="s">
+        <v>534</v>
+      </c>
+      <c r="B245" s="1" t="s">
         <v>535</v>
       </c>
-      <c r="B245" s="1" t="s">
-        <v>536</v>
-      </c>
       <c r="C245" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D245" s="1" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="E245" s="1" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="F245" s="1" t="s">
         <v>5</v>
@@ -7289,19 +7286,19 @@
     </row>
     <row r="246" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A246" s="1" t="s">
+        <v>536</v>
+      </c>
+      <c r="B246" s="1" t="s">
         <v>537</v>
       </c>
-      <c r="B246" s="1" t="s">
-        <v>538</v>
-      </c>
       <c r="C246" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D246" s="1" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="E246" s="1" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="F246" s="1" t="s">
         <v>5</v>
@@ -7309,19 +7306,19 @@
     </row>
     <row r="247" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A247" s="1" t="s">
+        <v>538</v>
+      </c>
+      <c r="B247" s="1" t="s">
         <v>539</v>
       </c>
-      <c r="B247" s="1" t="s">
-        <v>540</v>
-      </c>
       <c r="C247" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D247" s="1" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="E247" s="1" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="F247" s="1" t="s">
         <v>5</v>
@@ -7329,79 +7326,79 @@
     </row>
     <row r="248" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A248" s="1" t="s">
+        <v>540</v>
+      </c>
+      <c r="B248" s="1" t="s">
         <v>541</v>
       </c>
-      <c r="B248" s="1" t="s">
-        <v>542</v>
-      </c>
       <c r="C248" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D248" s="1" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="E248" s="1" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="F248" s="1" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
     </row>
     <row r="249" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A249" s="1" t="s">
+        <v>542</v>
+      </c>
+      <c r="B249" s="1" t="s">
         <v>543</v>
       </c>
-      <c r="B249" s="1" t="s">
-        <v>544</v>
-      </c>
       <c r="C249" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D249" s="1" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="E249" s="1" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="F249" s="1" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
     </row>
     <row r="250" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A250" s="1" t="s">
+        <v>544</v>
+      </c>
+      <c r="B250" s="1" t="s">
         <v>545</v>
       </c>
-      <c r="B250" s="1" t="s">
-        <v>546</v>
-      </c>
       <c r="C250" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D250" s="1" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="E250" s="1" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="F250" s="1" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
     </row>
     <row r="251" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A251" s="1" t="s">
+        <v>546</v>
+      </c>
+      <c r="B251" s="1" t="s">
         <v>547</v>
       </c>
-      <c r="B251" s="1" t="s">
-        <v>548</v>
-      </c>
       <c r="C251" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D251" s="1" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="E251" s="1" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="F251" s="1" t="s">
         <v>79</v>
@@ -7409,19 +7406,19 @@
     </row>
     <row r="252" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A252" s="1" t="s">
+        <v>548</v>
+      </c>
+      <c r="B252" s="1" t="s">
         <v>549</v>
       </c>
-      <c r="B252" s="1" t="s">
-        <v>550</v>
-      </c>
       <c r="C252" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D252" s="1" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="E252" s="1" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="F252" s="1" t="s">
         <v>79</v>
@@ -7429,96 +7426,96 @@
     </row>
     <row r="253" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A253" s="1" t="s">
+        <v>550</v>
+      </c>
+      <c r="B253" s="1" t="s">
         <v>551</v>
       </c>
-      <c r="B253" s="1" t="s">
+      <c r="C253" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D253" s="1" t="s">
         <v>552</v>
-      </c>
-      <c r="C253" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D253" s="1" t="s">
-        <v>553</v>
       </c>
       <c r="E253" s="1" t="s">
         <v>4</v>
       </c>
       <c r="F253" s="1" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
     </row>
     <row r="254" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A254" s="1" t="s">
+        <v>553</v>
+      </c>
+      <c r="B254" s="1" t="s">
         <v>554</v>
       </c>
-      <c r="B254" s="1" t="s">
-        <v>555</v>
-      </c>
       <c r="C254" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D254" s="1" t="s">
-        <v>553</v>
+        <v>552</v>
       </c>
       <c r="E254" s="1" t="s">
         <v>8</v>
       </c>
       <c r="F254" s="1" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
     </row>
     <row r="255" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A255" s="1" t="s">
+        <v>555</v>
+      </c>
+      <c r="B255" s="1" t="s">
         <v>556</v>
       </c>
-      <c r="B255" s="1" t="s">
-        <v>557</v>
-      </c>
       <c r="C255" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D255" s="1" t="s">
-        <v>553</v>
+        <v>552</v>
       </c>
       <c r="E255" s="1" t="s">
         <v>11</v>
       </c>
       <c r="F255" s="1" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
     </row>
     <row r="256" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A256" s="1" t="s">
+        <v>557</v>
+      </c>
+      <c r="B256" s="1" t="s">
         <v>558</v>
       </c>
-      <c r="B256" s="1" t="s">
-        <v>559</v>
-      </c>
       <c r="C256" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D256" s="1" t="s">
-        <v>553</v>
+        <v>552</v>
       </c>
       <c r="E256" s="1" t="s">
         <v>14</v>
       </c>
       <c r="F256" s="1" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
     </row>
     <row r="257" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A257" s="1" t="s">
+        <v>559</v>
+      </c>
+      <c r="B257" s="1" t="s">
         <v>560</v>
       </c>
-      <c r="B257" s="1" t="s">
-        <v>561</v>
-      </c>
       <c r="C257" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D257" s="1" t="s">
-        <v>553</v>
+        <v>552</v>
       </c>
       <c r="E257" s="1" t="s">
         <v>18</v>
@@ -7529,16 +7526,16 @@
     </row>
     <row r="258" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A258" s="1" t="s">
+        <v>561</v>
+      </c>
+      <c r="B258" s="1" t="s">
         <v>562</v>
       </c>
-      <c r="B258" s="1" t="s">
-        <v>563</v>
-      </c>
       <c r="C258" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D258" s="1" t="s">
-        <v>553</v>
+        <v>552</v>
       </c>
       <c r="E258" s="1" t="s">
         <v>32</v>
@@ -7549,16 +7546,16 @@
     </row>
     <row r="259" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A259" s="1" t="s">
+        <v>563</v>
+      </c>
+      <c r="B259" s="1" t="s">
         <v>564</v>
       </c>
-      <c r="B259" s="1" t="s">
-        <v>565</v>
-      </c>
       <c r="C259" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D259" s="1" t="s">
-        <v>553</v>
+        <v>552</v>
       </c>
       <c r="E259" s="1" t="s">
         <v>35</v>
@@ -7569,16 +7566,16 @@
     </row>
     <row r="260" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A260" s="1" t="s">
+        <v>565</v>
+      </c>
+      <c r="B260" s="1" t="s">
         <v>566</v>
       </c>
-      <c r="B260" s="1" t="s">
-        <v>567</v>
-      </c>
       <c r="C260" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D260" s="1" t="s">
-        <v>553</v>
+        <v>552</v>
       </c>
       <c r="E260" s="1" t="s">
         <v>38</v>
@@ -7589,96 +7586,96 @@
     </row>
     <row r="261" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A261" s="1" t="s">
+        <v>567</v>
+      </c>
+      <c r="B261" s="1" t="s">
         <v>568</v>
       </c>
-      <c r="B261" s="1" t="s">
-        <v>569</v>
-      </c>
       <c r="C261" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D261" s="1" t="s">
-        <v>553</v>
+        <v>552</v>
       </c>
       <c r="E261" s="1" t="s">
         <v>58</v>
       </c>
       <c r="F261" s="1" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
     </row>
     <row r="262" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A262" s="1" t="s">
+        <v>569</v>
+      </c>
+      <c r="B262" s="1" t="s">
         <v>570</v>
       </c>
-      <c r="B262" s="1" t="s">
-        <v>571</v>
-      </c>
       <c r="C262" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D262" s="1" t="s">
-        <v>553</v>
+        <v>552</v>
       </c>
       <c r="E262" s="1" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="F262" s="1" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
     </row>
     <row r="263" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A263" s="1" t="s">
+        <v>571</v>
+      </c>
+      <c r="B263" s="1" t="s">
         <v>572</v>
       </c>
-      <c r="B263" s="1" t="s">
-        <v>573</v>
-      </c>
       <c r="C263" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D263" s="1" t="s">
-        <v>553</v>
+        <v>552</v>
       </c>
       <c r="E263" s="1" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="F263" s="1" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
     </row>
     <row r="264" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A264" s="1" t="s">
+        <v>573</v>
+      </c>
+      <c r="B264" s="1" t="s">
         <v>574</v>
       </c>
-      <c r="B264" s="1" t="s">
-        <v>575</v>
-      </c>
       <c r="C264" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D264" s="1" t="s">
-        <v>553</v>
+        <v>552</v>
       </c>
       <c r="E264" s="1" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="F264" s="1" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
     </row>
     <row r="265" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A265" s="1" t="s">
+        <v>575</v>
+      </c>
+      <c r="B265" s="1" t="s">
         <v>576</v>
       </c>
-      <c r="B265" s="1" t="s">
+      <c r="C265" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D265" s="1" t="s">
         <v>577</v>
-      </c>
-      <c r="C265" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D265" s="1" t="s">
-        <v>578</v>
       </c>
       <c r="E265" s="1" t="s">
         <v>4</v>
@@ -7689,16 +7686,16 @@
     </row>
     <row r="266" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A266" s="1" t="s">
+        <v>578</v>
+      </c>
+      <c r="B266" s="1" t="s">
         <v>579</v>
       </c>
-      <c r="B266" s="1" t="s">
-        <v>580</v>
-      </c>
       <c r="C266" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D266" s="1" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="E266" s="1" t="s">
         <v>8</v>
@@ -7709,136 +7706,136 @@
     </row>
     <row r="267" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A267" s="1" t="s">
+        <v>580</v>
+      </c>
+      <c r="B267" s="1" t="s">
         <v>581</v>
       </c>
-      <c r="B267" s="1" t="s">
-        <v>582</v>
-      </c>
       <c r="C267" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D267" s="1" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="E267" s="1" t="s">
         <v>11</v>
       </c>
       <c r="F267" s="1" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
     </row>
     <row r="268" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A268" s="1" t="s">
+        <v>582</v>
+      </c>
+      <c r="B268" s="1" t="s">
         <v>583</v>
       </c>
-      <c r="B268" s="1" t="s">
-        <v>584</v>
-      </c>
       <c r="C268" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D268" s="1" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="E268" s="1" t="s">
         <v>14</v>
       </c>
       <c r="F268" s="1" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
     </row>
     <row r="269" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A269" s="1" t="s">
+        <v>584</v>
+      </c>
+      <c r="B269" s="1" t="s">
         <v>585</v>
       </c>
-      <c r="B269" s="1" t="s">
-        <v>586</v>
-      </c>
       <c r="C269" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D269" s="1" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="E269" s="1" t="s">
         <v>18</v>
       </c>
       <c r="F269" s="1" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
     </row>
     <row r="270" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A270" s="1" t="s">
+        <v>586</v>
+      </c>
+      <c r="B270" s="1" t="s">
         <v>587</v>
       </c>
-      <c r="B270" s="1" t="s">
-        <v>588</v>
-      </c>
       <c r="C270" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D270" s="1" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="E270" s="1" t="s">
         <v>32</v>
       </c>
       <c r="F270" s="1" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
     </row>
     <row r="271" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A271" s="1" t="s">
+        <v>588</v>
+      </c>
+      <c r="B271" s="1" t="s">
         <v>589</v>
       </c>
-      <c r="B271" s="1" t="s">
-        <v>590</v>
-      </c>
       <c r="C271" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D271" s="1" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="E271" s="1" t="s">
         <v>35</v>
       </c>
       <c r="F271" s="1" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
     </row>
     <row r="272" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A272" s="1" t="s">
+        <v>590</v>
+      </c>
+      <c r="B272" s="1" t="s">
         <v>591</v>
       </c>
-      <c r="B272" s="1" t="s">
-        <v>592</v>
-      </c>
       <c r="C272" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D272" s="1" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="E272" s="1" t="s">
         <v>38</v>
       </c>
       <c r="F272" s="1" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
     </row>
     <row r="273" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A273" s="1" t="s">
+        <v>592</v>
+      </c>
+      <c r="B273" s="1" t="s">
         <v>593</v>
       </c>
-      <c r="B273" s="1" t="s">
-        <v>594</v>
-      </c>
       <c r="C273" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D273" s="1" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="E273" s="1" t="s">
         <v>58</v>
@@ -7849,19 +7846,19 @@
     </row>
     <row r="274" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A274" s="1" t="s">
+        <v>594</v>
+      </c>
+      <c r="B274" s="1" t="s">
         <v>595</v>
       </c>
-      <c r="B274" s="1" t="s">
-        <v>596</v>
-      </c>
       <c r="C274" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D274" s="1" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="E274" s="1" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="F274" s="1" t="s">
         <v>5</v>
@@ -7869,19 +7866,19 @@
     </row>
     <row r="275" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A275" s="1" t="s">
+        <v>596</v>
+      </c>
+      <c r="B275" s="1" t="s">
         <v>597</v>
       </c>
-      <c r="B275" s="1" t="s">
-        <v>598</v>
-      </c>
       <c r="C275" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D275" s="1" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="E275" s="1" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="F275" s="1" t="s">
         <v>5</v>
@@ -7889,19 +7886,19 @@
     </row>
     <row r="276" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A276" s="1" t="s">
+        <v>598</v>
+      </c>
+      <c r="B276" s="1" t="s">
         <v>599</v>
       </c>
-      <c r="B276" s="1" t="s">
-        <v>600</v>
-      </c>
       <c r="C276" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D276" s="1" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="E276" s="1" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="F276" s="1" t="s">
         <v>79</v>
@@ -7909,19 +7906,19 @@
     </row>
     <row r="277" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A277" s="1" t="s">
+        <v>600</v>
+      </c>
+      <c r="B277" s="1" t="s">
         <v>601</v>
       </c>
-      <c r="B277" s="1" t="s">
-        <v>602</v>
-      </c>
       <c r="C277" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D277" s="1" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="E277" s="1" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="F277" s="1" t="s">
         <v>79</v>
@@ -7929,156 +7926,156 @@
     </row>
     <row r="278" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A278" s="1" t="s">
+        <v>602</v>
+      </c>
+      <c r="B278" s="1" t="s">
         <v>603</v>
       </c>
-      <c r="B278" s="1" t="s">
+      <c r="C278" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D278" s="1" t="s">
         <v>604</v>
-      </c>
-      <c r="C278" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D278" s="1" t="s">
-        <v>605</v>
       </c>
       <c r="E278" s="1" t="s">
         <v>4</v>
       </c>
       <c r="F278" s="1" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
     </row>
     <row r="279" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A279" s="1" t="s">
+        <v>605</v>
+      </c>
+      <c r="B279" s="1" t="s">
         <v>606</v>
       </c>
-      <c r="B279" s="1" t="s">
-        <v>607</v>
-      </c>
       <c r="C279" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D279" s="1" t="s">
-        <v>605</v>
+        <v>604</v>
       </c>
       <c r="E279" s="1" t="s">
         <v>8</v>
       </c>
       <c r="F279" s="1" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
     </row>
     <row r="280" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A280" s="1" t="s">
+        <v>607</v>
+      </c>
+      <c r="B280" s="1" t="s">
         <v>608</v>
       </c>
-      <c r="B280" s="1" t="s">
-        <v>609</v>
-      </c>
       <c r="C280" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D280" s="1" t="s">
-        <v>605</v>
+        <v>604</v>
       </c>
       <c r="E280" s="1" t="s">
         <v>11</v>
       </c>
       <c r="F280" s="1" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
     </row>
     <row r="281" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A281" s="1" t="s">
+        <v>609</v>
+      </c>
+      <c r="B281" s="1" t="s">
         <v>610</v>
       </c>
-      <c r="B281" s="1" t="s">
-        <v>611</v>
-      </c>
       <c r="C281" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D281" s="1" t="s">
-        <v>605</v>
+        <v>604</v>
       </c>
       <c r="E281" s="1" t="s">
         <v>14</v>
       </c>
       <c r="F281" s="1" t="s">
-        <v>612</v>
+        <v>611</v>
       </c>
     </row>
     <row r="282" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A282" s="1" t="s">
+        <v>612</v>
+      </c>
+      <c r="B282" s="1" t="s">
         <v>613</v>
       </c>
-      <c r="B282" s="1" t="s">
-        <v>614</v>
-      </c>
       <c r="C282" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D282" s="1" t="s">
-        <v>605</v>
+        <v>604</v>
       </c>
       <c r="E282" s="1" t="s">
         <v>18</v>
       </c>
       <c r="F282" s="1" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
     </row>
     <row r="283" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A283" s="1" t="s">
+        <v>614</v>
+      </c>
+      <c r="B283" s="1" t="s">
         <v>615</v>
       </c>
-      <c r="B283" s="1" t="s">
-        <v>616</v>
-      </c>
       <c r="C283" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D283" s="1" t="s">
-        <v>605</v>
+        <v>604</v>
       </c>
       <c r="E283" s="1" t="s">
         <v>32</v>
       </c>
       <c r="F283" s="1" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
     </row>
     <row r="284" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A284" s="1" t="s">
+        <v>616</v>
+      </c>
+      <c r="B284" s="1" t="s">
         <v>617</v>
       </c>
-      <c r="B284" s="1" t="s">
-        <v>618</v>
-      </c>
       <c r="C284" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D284" s="1" t="s">
-        <v>605</v>
+        <v>604</v>
       </c>
       <c r="E284" s="1" t="s">
         <v>35</v>
       </c>
       <c r="F284" s="1" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
     </row>
     <row r="285" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A285" s="1" t="s">
+        <v>618</v>
+      </c>
+      <c r="B285" s="1" t="s">
         <v>619</v>
       </c>
-      <c r="B285" s="1" t="s">
-        <v>620</v>
-      </c>
       <c r="C285" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D285" s="1" t="s">
-        <v>605</v>
+        <v>604</v>
       </c>
       <c r="E285" s="1" t="s">
         <v>38</v>
@@ -8089,59 +8086,59 @@
     </row>
     <row r="286" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A286" s="1" t="s">
+        <v>620</v>
+      </c>
+      <c r="B286" s="1" t="s">
         <v>621</v>
       </c>
-      <c r="B286" s="1" t="s">
-        <v>622</v>
-      </c>
       <c r="C286" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D286" s="1" t="s">
-        <v>605</v>
+        <v>604</v>
       </c>
       <c r="E286" s="1" t="s">
         <v>58</v>
       </c>
       <c r="F286" s="1" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
     </row>
     <row r="287" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A287" s="1" t="s">
+        <v>622</v>
+      </c>
+      <c r="B287" s="1" t="s">
         <v>623</v>
       </c>
-      <c r="B287" s="1" t="s">
-        <v>624</v>
-      </c>
       <c r="C287" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D287" s="1" t="s">
-        <v>605</v>
+        <v>604</v>
       </c>
       <c r="E287" s="1" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="F287" s="1" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
     </row>
     <row r="288" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A288" s="1" t="s">
+        <v>624</v>
+      </c>
+      <c r="B288" s="1" t="s">
         <v>625</v>
       </c>
-      <c r="B288" s="1" t="s">
-        <v>626</v>
-      </c>
       <c r="C288" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D288" s="1" t="s">
-        <v>605</v>
+        <v>604</v>
       </c>
       <c r="E288" s="1" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="F288" s="1" t="s">
         <v>5</v>
@@ -8149,19 +8146,19 @@
     </row>
     <row r="289" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A289" s="1" t="s">
+        <v>626</v>
+      </c>
+      <c r="B289" s="1" t="s">
         <v>627</v>
       </c>
-      <c r="B289" s="1" t="s">
-        <v>628</v>
-      </c>
       <c r="C289" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D289" s="1" t="s">
-        <v>605</v>
+        <v>604</v>
       </c>
       <c r="E289" s="1" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="F289" s="1" t="s">
         <v>5</v>
@@ -8169,96 +8166,96 @@
     </row>
     <row r="290" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A290" s="1" t="s">
+        <v>628</v>
+      </c>
+      <c r="B290" s="1" t="s">
         <v>629</v>
       </c>
-      <c r="B290" s="1" t="s">
-        <v>630</v>
-      </c>
       <c r="C290" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D290" s="1" t="s">
-        <v>605</v>
+        <v>604</v>
       </c>
       <c r="E290" s="1" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="F290" s="1" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
     </row>
     <row r="291" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A291" s="1" t="s">
+        <v>630</v>
+      </c>
+      <c r="B291" s="1" t="s">
         <v>631</v>
       </c>
-      <c r="B291" s="1" t="s">
+      <c r="C291" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D291" s="1" t="s">
         <v>632</v>
-      </c>
-      <c r="C291" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D291" s="1" t="s">
-        <v>633</v>
       </c>
       <c r="E291" s="1" t="s">
         <v>4</v>
       </c>
       <c r="F291" s="1" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
     </row>
     <row r="292" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A292" s="1" t="s">
+        <v>633</v>
+      </c>
+      <c r="B292" s="1" t="s">
         <v>634</v>
       </c>
-      <c r="B292" s="1" t="s">
-        <v>635</v>
-      </c>
       <c r="C292" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D292" s="1" t="s">
-        <v>633</v>
+        <v>632</v>
       </c>
       <c r="E292" s="1" t="s">
         <v>8</v>
       </c>
       <c r="F292" s="1" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
     </row>
     <row r="293" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A293" s="1" t="s">
+        <v>635</v>
+      </c>
+      <c r="B293" s="1" t="s">
         <v>636</v>
       </c>
-      <c r="B293" s="1" t="s">
-        <v>637</v>
-      </c>
       <c r="C293" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D293" s="1" t="s">
-        <v>633</v>
+        <v>632</v>
       </c>
       <c r="E293" s="1" t="s">
         <v>11</v>
       </c>
       <c r="F293" s="1" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
     </row>
     <row r="294" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A294" s="1" t="s">
+        <v>637</v>
+      </c>
+      <c r="B294" s="1" t="s">
         <v>638</v>
       </c>
-      <c r="B294" s="1" t="s">
-        <v>639</v>
-      </c>
       <c r="C294" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D294" s="1" t="s">
-        <v>633</v>
+        <v>632</v>
       </c>
       <c r="E294" s="1" t="s">
         <v>14</v>
@@ -8269,96 +8266,96 @@
     </row>
     <row r="295" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A295" s="1" t="s">
+        <v>639</v>
+      </c>
+      <c r="B295" s="1" t="s">
         <v>640</v>
       </c>
-      <c r="B295" s="1" t="s">
-        <v>641</v>
-      </c>
       <c r="C295" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D295" s="1" t="s">
-        <v>633</v>
+        <v>632</v>
       </c>
       <c r="E295" s="1" t="s">
         <v>18</v>
       </c>
       <c r="F295" s="1" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
     </row>
     <row r="296" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A296" s="1" t="s">
+        <v>641</v>
+      </c>
+      <c r="B296" s="1" t="s">
         <v>642</v>
       </c>
-      <c r="B296" s="1" t="s">
-        <v>643</v>
-      </c>
       <c r="C296" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D296" s="1" t="s">
-        <v>633</v>
+        <v>632</v>
       </c>
       <c r="E296" s="1" t="s">
         <v>32</v>
       </c>
       <c r="F296" s="1" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
     </row>
     <row r="297" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A297" s="1" t="s">
+        <v>643</v>
+      </c>
+      <c r="B297" s="1" t="s">
         <v>644</v>
       </c>
-      <c r="B297" s="1" t="s">
-        <v>645</v>
-      </c>
       <c r="C297" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D297" s="1" t="s">
-        <v>633</v>
+        <v>632</v>
       </c>
       <c r="E297" s="1" t="s">
         <v>35</v>
       </c>
       <c r="F297" s="1" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
     </row>
     <row r="298" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A298" s="1" t="s">
+        <v>645</v>
+      </c>
+      <c r="B298" s="1" t="s">
         <v>646</v>
       </c>
-      <c r="B298" s="1" t="s">
-        <v>647</v>
-      </c>
       <c r="C298" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D298" s="1" t="s">
-        <v>633</v>
+        <v>632</v>
       </c>
       <c r="E298" s="1" t="s">
         <v>38</v>
       </c>
       <c r="F298" s="1" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
     </row>
     <row r="299" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A299" s="1" t="s">
+        <v>647</v>
+      </c>
+      <c r="B299" s="1" t="s">
         <v>648</v>
       </c>
-      <c r="B299" s="1" t="s">
-        <v>649</v>
-      </c>
       <c r="C299" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D299" s="1" t="s">
-        <v>633</v>
+        <v>632</v>
       </c>
       <c r="E299" s="1" t="s">
         <v>58</v>
@@ -8369,19 +8366,19 @@
     </row>
     <row r="300" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A300" s="1" t="s">
+        <v>649</v>
+      </c>
+      <c r="B300" s="1" t="s">
         <v>650</v>
       </c>
-      <c r="B300" s="1" t="s">
-        <v>651</v>
-      </c>
       <c r="C300" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D300" s="1" t="s">
-        <v>633</v>
+        <v>632</v>
       </c>
       <c r="E300" s="1" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="F300" s="1" t="s">
         <v>5</v>
@@ -8389,19 +8386,19 @@
     </row>
     <row r="301" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A301" s="1" t="s">
+        <v>651</v>
+      </c>
+      <c r="B301" s="1" t="s">
         <v>652</v>
       </c>
-      <c r="B301" s="1" t="s">
-        <v>653</v>
-      </c>
       <c r="C301" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D301" s="1" t="s">
-        <v>633</v>
+        <v>632</v>
       </c>
       <c r="E301" s="1" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="F301" s="1" t="s">
         <v>5</v>
@@ -8409,19 +8406,19 @@
     </row>
     <row r="302" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A302" s="1" t="s">
+        <v>653</v>
+      </c>
+      <c r="B302" s="1" t="s">
         <v>654</v>
       </c>
-      <c r="B302" s="1" t="s">
-        <v>655</v>
-      </c>
       <c r="C302" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D302" s="1" t="s">
-        <v>633</v>
+        <v>632</v>
       </c>
       <c r="E302" s="1" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="F302" s="1" t="s">
         <v>5</v>
@@ -8429,19 +8426,19 @@
     </row>
     <row r="303" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A303" s="1" t="s">
+        <v>655</v>
+      </c>
+      <c r="B303" s="1" t="s">
         <v>656</v>
       </c>
-      <c r="B303" s="1" t="s">
-        <v>657</v>
-      </c>
       <c r="C303" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D303" s="1" t="s">
-        <v>633</v>
+        <v>632</v>
       </c>
       <c r="E303" s="1" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="F303" s="1" t="s">
         <v>105</v>
